--- a/HNM03S.xlsx
+++ b/HNM03S.xlsx
@@ -1,34 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{1987CAB6-5110-C547-99DF-7EC1A6B0541F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="406">
   <si>
     <t/>
   </si>
@@ -558,6 +541,12 @@
     <t>CAT CHZE+ TN&amp;MRL 500</t>
   </si>
   <si>
+    <t>20134229</t>
+  </si>
+  <si>
+    <t>ME-O TUNA IN JLY 400</t>
+  </si>
+  <si>
     <t>20134226</t>
   </si>
   <si>
@@ -708,12 +697,6 @@
     <t>ME-O KTN OCN.FISH 50</t>
   </si>
   <si>
-    <t>20134229</t>
-  </si>
-  <si>
-    <t>ME-O TUNA IN JLY 400</t>
-  </si>
-  <si>
     <t>20128695</t>
   </si>
   <si>
@@ -1246,22 +1229,19 @@
   </si>
   <si>
     <t>31</t>
-  </si>
-  <si>
-    <t>HNM03S_2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1282,16 +1262,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="000000"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="000000"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1640,18 +1620,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F185"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="9.953125" customWidth="1"/>
-    <col min="2" max="2" width="22.05859375" customWidth="1"/>
-    <col min="3" max="3" width="7.93359375" customWidth="1"/>
-    <col min="4" max="5" width="4.03515625" customWidth="1"/>
-    <col min="6" max="6" width="11.02734375" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="5" width="4" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1671,7 +1651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1691,7 +1671,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1711,7 +1691,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1731,7 +1711,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -1751,7 +1731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -1771,7 +1751,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -1791,7 +1771,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
@@ -1811,7 +1791,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
@@ -1831,7 +1811,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
@@ -1851,7 +1831,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>28</v>
       </c>
@@ -1871,7 +1851,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>30</v>
       </c>
@@ -1891,7 +1871,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>33</v>
       </c>
@@ -1911,7 +1891,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>35</v>
       </c>
@@ -1931,7 +1911,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>37</v>
       </c>
@@ -1951,7 +1931,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>39</v>
       </c>
@@ -1971,7 +1951,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>42</v>
       </c>
@@ -1991,7 +1971,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>44</v>
       </c>
@@ -2011,7 +1991,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>46</v>
       </c>
@@ -2031,7 +2011,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>48</v>
       </c>
@@ -2051,7 +2031,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>50</v>
       </c>
@@ -2071,7 +2051,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>52</v>
       </c>
@@ -2091,7 +2071,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>54</v>
       </c>
@@ -2111,7 +2091,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>56</v>
       </c>
@@ -2131,7 +2111,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>58</v>
       </c>
@@ -2151,7 +2131,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>61</v>
       </c>
@@ -2171,7 +2151,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>63</v>
       </c>
@@ -2191,7 +2171,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>66</v>
       </c>
@@ -2211,7 +2191,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>69</v>
       </c>
@@ -2231,7 +2211,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>71</v>
       </c>
@@ -2251,7 +2231,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>73</v>
       </c>
@@ -2271,7 +2251,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>75</v>
       </c>
@@ -2291,7 +2271,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>77</v>
       </c>
@@ -2311,7 +2291,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>79</v>
       </c>
@@ -2331,7 +2311,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>81</v>
       </c>
@@ -2351,7 +2331,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>83</v>
       </c>
@@ -2371,7 +2351,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>85</v>
       </c>
@@ -2391,7 +2371,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>87</v>
       </c>
@@ -2411,7 +2391,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>89</v>
       </c>
@@ -2431,7 +2411,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>91</v>
       </c>
@@ -2451,7 +2431,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>93</v>
       </c>
@@ -2471,7 +2451,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>95</v>
       </c>
@@ -2491,7 +2471,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>97</v>
       </c>
@@ -2511,7 +2491,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>99</v>
       </c>
@@ -2531,7 +2511,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>102</v>
       </c>
@@ -2551,7 +2531,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>104</v>
       </c>
@@ -2571,7 +2551,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>107</v>
       </c>
@@ -2591,7 +2571,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>109</v>
       </c>
@@ -2611,7 +2591,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>111</v>
       </c>
@@ -2631,7 +2611,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>113</v>
       </c>
@@ -2651,7 +2631,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>115</v>
       </c>
@@ -2671,7 +2651,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>117</v>
       </c>
@@ -2691,7 +2671,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>119</v>
       </c>
@@ -2711,7 +2691,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>121</v>
       </c>
@@ -2731,7 +2711,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>123</v>
       </c>
@@ -2751,7 +2731,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>126</v>
       </c>
@@ -2771,7 +2751,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>128</v>
       </c>
@@ -2791,7 +2771,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>130</v>
       </c>
@@ -2811,7 +2791,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>132</v>
       </c>
@@ -2831,7 +2811,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>135</v>
       </c>
@@ -2851,7 +2831,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>137</v>
       </c>
@@ -2871,7 +2851,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>139</v>
       </c>
@@ -2891,7 +2871,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>141</v>
       </c>
@@ -2911,7 +2891,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>143</v>
       </c>
@@ -2931,7 +2911,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>145</v>
       </c>
@@ -2951,7 +2931,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>147</v>
       </c>
@@ -2971,7 +2951,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>149</v>
       </c>
@@ -2991,7 +2971,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>151</v>
       </c>
@@ -3011,7 +2991,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>153</v>
       </c>
@@ -3031,7 +3011,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>155</v>
       </c>
@@ -3051,7 +3031,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>157</v>
       </c>
@@ -3071,7 +3051,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>159</v>
       </c>
@@ -3091,7 +3071,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>161</v>
       </c>
@@ -3111,7 +3091,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>163</v>
       </c>
@@ -3131,7 +3111,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>165</v>
       </c>
@@ -3151,7 +3131,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>168</v>
       </c>
@@ -3171,7 +3151,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>170</v>
       </c>
@@ -3191,7 +3171,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>172</v>
       </c>
@@ -3211,7 +3191,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>174</v>
       </c>
@@ -3231,32 +3211,32 @@
         <v>106</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A80" s="1">
-        <v>20134229</v>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>176</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>227</v>
+        <v>177</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="D80" s="1">
-        <v>8</v>
-      </c>
-      <c r="E80" s="1">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -3271,12 +3251,12 @@
         <v>125</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
@@ -3291,12 +3271,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
@@ -3311,12 +3291,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
@@ -3331,12 +3311,12 @@
         <v>101</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
@@ -3351,12 +3331,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
@@ -3371,12 +3351,12 @@
         <v>101</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -3388,15 +3368,15 @@
         <v>15</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -3408,15 +3388,15 @@
         <v>18</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3431,12 +3411,12 @@
         <v>101</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3451,12 +3431,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3471,12 +3451,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -3491,12 +3471,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3511,12 +3491,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3531,12 +3511,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3551,12 +3531,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3571,12 +3551,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3591,12 +3571,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3611,12 +3591,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -3631,12 +3611,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3651,12 +3631,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -3671,12 +3651,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -3688,15 +3668,15 @@
         <v>18</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
@@ -3711,12 +3691,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
@@ -3731,12 +3711,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>227</v>
+        <v>177</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -3751,7 +3731,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>228</v>
       </c>
@@ -3771,7 +3751,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>230</v>
       </c>
@@ -3791,7 +3771,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>232</v>
       </c>
@@ -3811,7 +3791,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>234</v>
       </c>
@@ -3831,7 +3811,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>237</v>
       </c>
@@ -3851,7 +3831,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>239</v>
       </c>
@@ -3871,7 +3851,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>241</v>
       </c>
@@ -3891,7 +3871,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>243</v>
       </c>
@@ -3911,7 +3891,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>245</v>
       </c>
@@ -3931,7 +3911,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>247</v>
       </c>
@@ -3951,7 +3931,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>249</v>
       </c>
@@ -3971,7 +3951,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>251</v>
       </c>
@@ -3991,7 +3971,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>253</v>
       </c>
@@ -4011,7 +3991,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>255</v>
       </c>
@@ -4031,7 +4011,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>257</v>
       </c>
@@ -4051,7 +4031,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>259</v>
       </c>
@@ -4071,7 +4051,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>261</v>
       </c>
@@ -4091,7 +4071,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>263</v>
       </c>
@@ -4111,7 +4091,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>265</v>
       </c>
@@ -4131,7 +4111,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>267</v>
       </c>
@@ -4151,7 +4131,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>269</v>
       </c>
@@ -4171,7 +4151,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>271</v>
       </c>
@@ -4191,7 +4171,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>273</v>
       </c>
@@ -4211,7 +4191,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>275</v>
       </c>
@@ -4231,7 +4211,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>277</v>
       </c>
@@ -4251,7 +4231,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>279</v>
       </c>
@@ -4271,7 +4251,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>281</v>
       </c>
@@ -4291,7 +4271,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>283</v>
       </c>
@@ -4311,7 +4291,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>285</v>
       </c>
@@ -4331,7 +4311,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>288</v>
       </c>
@@ -4351,7 +4331,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>290</v>
       </c>
@@ -4371,7 +4351,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>292</v>
       </c>
@@ -4391,7 +4371,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>294</v>
       </c>
@@ -4411,7 +4391,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>296</v>
       </c>
@@ -4431,7 +4411,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>298</v>
       </c>
@@ -4451,7 +4431,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>300</v>
       </c>
@@ -4471,7 +4451,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>302</v>
       </c>
@@ -4491,7 +4471,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>304</v>
       </c>
@@ -4511,7 +4491,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>306</v>
       </c>
@@ -4531,7 +4511,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>309</v>
       </c>
@@ -4551,7 +4531,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>311</v>
       </c>
@@ -4571,7 +4551,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>313</v>
       </c>
@@ -4591,7 +4571,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>315</v>
       </c>
@@ -4611,7 +4591,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>317</v>
       </c>
@@ -4631,7 +4611,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>319</v>
       </c>
@@ -4651,7 +4631,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>321</v>
       </c>
@@ -4671,7 +4651,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>323</v>
       </c>
@@ -4691,7 +4671,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>325</v>
       </c>
@@ -4711,7 +4691,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>327</v>
       </c>
@@ -4731,7 +4711,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>329</v>
       </c>
@@ -4751,7 +4731,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>331</v>
       </c>
@@ -4771,7 +4751,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>333</v>
       </c>
@@ -4791,7 +4771,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>335</v>
       </c>
@@ -4811,7 +4791,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>338</v>
       </c>
@@ -4831,7 +4811,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>340</v>
       </c>
@@ -4851,7 +4831,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>342</v>
       </c>
@@ -4871,7 +4851,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>344</v>
       </c>
@@ -4891,7 +4871,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>346</v>
       </c>
@@ -4911,7 +4891,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>348</v>
       </c>
@@ -4931,7 +4911,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>350</v>
       </c>
@@ -4951,7 +4931,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>352</v>
       </c>
@@ -4971,7 +4951,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>354</v>
       </c>
@@ -4991,7 +4971,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>356</v>
       </c>
@@ -5011,7 +4991,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>358</v>
       </c>
@@ -5031,7 +5011,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>360</v>
       </c>
@@ -5051,7 +5031,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>362</v>
       </c>
@@ -5071,7 +5051,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>365</v>
       </c>
@@ -5091,7 +5071,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>367</v>
       </c>
@@ -5111,7 +5091,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>370</v>
       </c>
@@ -5131,7 +5111,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>373</v>
       </c>
@@ -5151,7 +5131,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>376</v>
       </c>
@@ -5171,7 +5151,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>379</v>
       </c>
@@ -5191,7 +5171,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>382</v>
       </c>
@@ -5211,7 +5191,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>385</v>
       </c>
@@ -5231,7 +5211,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>388</v>
       </c>
@@ -5251,7 +5231,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>391</v>
       </c>
@@ -5271,7 +5251,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>394</v>
       </c>
@@ -5291,7 +5271,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>397</v>
       </c>
@@ -5311,7 +5291,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>400</v>
       </c>
@@ -5331,7 +5311,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>403</v>
       </c>
@@ -5353,6 +5333,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/HNM03S.xlsx
+++ b/HNM03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="399">
   <si>
     <t/>
   </si>
@@ -73,57 +73,51 @@
     <t>RT</t>
   </si>
   <si>
-    <t>20082080</t>
-  </si>
-  <si>
-    <t>IDM ZIPPER BAG 25'S</t>
+    <t>20092994</t>
+  </si>
+  <si>
+    <t>IDM CLING WRAP 30X30</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>10014035</t>
+  </si>
+  <si>
+    <t>BAGUS SK.LANTAI20920</t>
+  </si>
+  <si>
+    <t>10014036</t>
+  </si>
+  <si>
+    <t>BAGUS SKT.BAJU 20930</t>
+  </si>
+  <si>
+    <t>20039156</t>
+  </si>
+  <si>
+    <t>IDM J/HJN DISP DWSA</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20140873</t>
+  </si>
+  <si>
+    <t>IDM JAS HJ.DISP STLN</t>
+  </si>
+  <si>
+    <t>20071123</t>
+  </si>
+  <si>
+    <t>IDM JAS HUJAN SETLN</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20092994</t>
-  </si>
-  <si>
-    <t>IDM CLING WRAP 30X30</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>10014035</t>
-  </si>
-  <si>
-    <t>BAGUS SK.LANTAI20920</t>
-  </si>
-  <si>
-    <t>10014036</t>
-  </si>
-  <si>
-    <t>BAGUS SKT.BAJU 20930</t>
-  </si>
-  <si>
-    <t>20039156</t>
-  </si>
-  <si>
-    <t>IDM J/HJN DISP DWSA</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20140873</t>
-  </si>
-  <si>
-    <t>IDM JAS HJ.DISP STLN</t>
-  </si>
-  <si>
-    <t>20071123</t>
-  </si>
-  <si>
-    <t>IDM JAS HUJAN SETLN</t>
-  </si>
-  <si>
     <t>20090053</t>
   </si>
   <si>
@@ -1018,21 +1012,15 @@
     <t>BRIGHT GAS KLG 220G</t>
   </si>
   <si>
-    <t>20035267</t>
-  </si>
-  <si>
-    <t>INDOMARET SAPU IJUK</t>
+    <t>20076488</t>
+  </si>
+  <si>
+    <t>IDM SAPU LIDI TABAH</t>
   </si>
   <si>
     <t>16</t>
   </si>
   <si>
-    <t>20076488</t>
-  </si>
-  <si>
-    <t>IDM SAPU LIDI TABAH</t>
-  </si>
-  <si>
     <t>20034850</t>
   </si>
   <si>
@@ -1121,15 +1109,6 @@
   </si>
   <si>
     <t>17</t>
-  </si>
-  <si>
-    <t>20072325</t>
-  </si>
-  <si>
-    <t>IDM SNDAL WNTA 37-38</t>
-  </si>
-  <si>
-    <t>19</t>
   </si>
   <si>
     <t>20037222</t>
@@ -1621,7 +1600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F185"/>
+  <dimension ref="A1:F182"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1788,7 +1767,7 @@
         <v>22</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1802,10 +1781,10 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>19</v>
@@ -1813,10 +1792,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -1825,7 +1804,7 @@
         <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>19</v>
@@ -1833,10 +1812,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -1845,10 +1824,10 @@
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1865,7 +1844,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>5</v>
@@ -1873,10 +1852,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -1885,7 +1864,7 @@
         <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -1908,7 +1887,7 @@
         <v>22</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1925,27 +1904,27 @@
         <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -1962,10 +1941,10 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -1982,10 +1961,10 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>5</v>
@@ -2002,13 +1981,13 @@
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2022,10 +2001,10 @@
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>19</v>
@@ -2042,10 +2021,10 @@
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>19</v>
@@ -2062,7 +2041,7 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>22</v>
@@ -2082,13 +2061,13 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2102,10 +2081,10 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -2113,19 +2092,19 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -2142,10 +2121,10 @@
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -2153,42 +2132,42 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2205,7 +2184,7 @@
         <v>15</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -2225,7 +2204,7 @@
         <v>15</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -2245,10 +2224,10 @@
         <v>15</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2265,7 +2244,7 @@
         <v>15</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>19</v>
@@ -2285,7 +2264,7 @@
         <v>15</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>19</v>
@@ -2308,7 +2287,7 @@
         <v>22</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2325,10 +2304,10 @@
         <v>15</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2342,13 +2321,13 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2365,7 +2344,7 @@
         <v>18</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -2385,10 +2364,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2405,7 +2384,7 @@
         <v>18</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>19</v>
@@ -2425,7 +2404,7 @@
         <v>18</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>19</v>
@@ -2448,7 +2427,7 @@
         <v>22</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2465,7 +2444,7 @@
         <v>18</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -2482,33 +2461,33 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2522,33 +2501,33 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2562,13 +2541,13 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2582,13 +2561,13 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2602,13 +2581,13 @@
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>106</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2622,7 +2601,7 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>15</v>
@@ -2642,10 +2621,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>19</v>
@@ -2662,10 +2641,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>19</v>
@@ -2682,10 +2661,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>19</v>
@@ -2702,33 +2681,33 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F55" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2742,13 +2721,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2762,13 +2741,13 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2782,33 +2761,33 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2822,13 +2801,13 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>134</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2842,10 +2821,10 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>19</v>
@@ -2865,7 +2844,7 @@
         <v>22</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>19</v>
@@ -2882,13 +2861,13 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>19</v>
+        <v>104</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2902,13 +2881,13 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>106</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2922,10 +2901,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>19</v>
@@ -2942,10 +2921,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>19</v>
@@ -2962,10 +2941,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>19</v>
@@ -2982,10 +2961,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>19</v>
@@ -3002,7 +2981,7 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>22</v>
@@ -3022,10 +3001,10 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>19</v>
@@ -3042,10 +3021,10 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>19</v>
@@ -3062,13 +3041,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>19</v>
+        <v>132</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3082,13 +3061,13 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -3102,33 +3081,33 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>68</v>
+        <v>165</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>134</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>167</v>
+        <v>4</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>19</v>
+        <v>104</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3142,13 +3121,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3162,13 +3141,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3182,13 +3161,13 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3202,13 +3181,13 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3222,13 +3201,13 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3242,13 +3221,13 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3262,13 +3241,13 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3282,13 +3261,13 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3302,13 +3281,13 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3322,13 +3301,13 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3342,33 +3321,33 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>101</v>
+        <v>190</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F87" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3382,13 +3361,13 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>192</v>
+        <v>99</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3402,13 +3381,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3422,13 +3401,13 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3442,13 +3421,13 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3462,13 +3441,13 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3482,13 +3461,13 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3502,13 +3481,13 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3522,13 +3501,13 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3542,13 +3521,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3562,13 +3541,13 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3582,13 +3561,13 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3602,13 +3581,13 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3622,13 +3601,13 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3642,33 +3621,33 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>106</v>
+        <v>221</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>223</v>
+        <v>104</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3682,53 +3661,53 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>226</v>
+        <v>174</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>227</v>
+        <v>175</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>176</v>
+        <v>226</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>177</v>
+        <v>227</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3742,13 +3721,13 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3762,13 +3741,13 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3782,33 +3761,33 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>106</v>
+        <v>234</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>236</v>
+        <v>104</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3822,13 +3801,13 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3842,13 +3821,13 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3862,13 +3841,13 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>68</v>
+        <v>165</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3882,13 +3861,13 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>167</v>
+        <v>4</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>125</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3902,10 +3881,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3922,10 +3901,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3942,10 +3921,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3962,10 +3941,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3982,10 +3961,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -4002,7 +3981,7 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>22</v>
@@ -4022,13 +4001,13 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>68</v>
+        <v>165</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>5</v>
+        <v>234</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4042,13 +4021,13 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>236</v>
+        <v>99</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4062,13 +4041,13 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>101</v>
+        <v>234</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4082,13 +4061,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4102,13 +4081,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4122,13 +4101,13 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>236</v>
+        <v>99</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4142,13 +4121,13 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>101</v>
+        <v>19</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4162,13 +4141,13 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -4182,13 +4161,13 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>101</v>
+        <v>19</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4202,13 +4181,13 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4222,7 +4201,7 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>22</v>
@@ -4242,10 +4221,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -4262,10 +4241,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4282,10 +4261,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>167</v>
+        <v>285</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4293,22 +4272,22 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="E134" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4322,10 +4301,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>19</v>
@@ -4342,10 +4321,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>19</v>
@@ -4362,10 +4341,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>19</v>
@@ -4382,10 +4361,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>19</v>
@@ -4402,7 +4381,7 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>22</v>
@@ -4422,13 +4401,13 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4442,13 +4421,13 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4462,10 +4441,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>19</v>
@@ -4482,30 +4461,30 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>287</v>
+        <v>306</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D144" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>308</v>
-      </c>
       <c r="E144" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4522,10 +4501,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4542,10 +4521,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4562,10 +4541,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4582,13 +4561,13 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4602,7 +4581,7 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>22</v>
@@ -4622,10 +4601,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>19</v>
@@ -4642,10 +4621,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>19</v>
@@ -4662,10 +4641,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>19</v>
@@ -4682,10 +4661,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>19</v>
@@ -4702,10 +4681,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>68</v>
+        <v>165</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>19</v>
@@ -4722,13 +4701,13 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>167</v>
+        <v>285</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>19</v>
+        <v>234</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4742,13 +4721,13 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>287</v>
+        <v>306</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>236</v>
+        <v>5</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4762,10 +4741,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>308</v>
+        <v>335</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>308</v>
+        <v>29</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4773,19 +4752,19 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="E158" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4802,10 +4781,10 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4822,13 +4801,13 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -4842,13 +4821,13 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4862,10 +4841,10 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>19</v>
@@ -4882,13 +4861,13 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -4902,10 +4881,10 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>19</v>
@@ -4922,13 +4901,13 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -4942,10 +4921,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>65</v>
+        <v>165</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>19</v>
@@ -4962,10 +4941,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>68</v>
+        <v>285</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>19</v>
@@ -4982,10 +4961,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>167</v>
+        <v>306</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>19</v>
@@ -5002,10 +4981,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>287</v>
+        <v>360</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>19</v>
@@ -5013,79 +4992,79 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>308</v>
+        <v>335</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>337</v>
+        <v>368</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5093,19 +5072,19 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5113,39 +5092,39 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5153,79 +5132,79 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>19</v>
@@ -5233,19 +5212,19 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>19</v>
@@ -5253,81 +5232,21 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A183" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="F183" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A184" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="B184" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="E184" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="F184" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A185" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="E185" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="F185" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/HNM03S.xlsx
+++ b/HNM03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="405">
   <si>
     <t/>
   </si>
@@ -304,15 +304,21 @@
     <t>IDM SPONGE MANDI PCK</t>
   </si>
   <si>
+    <t>20141993</t>
+  </si>
+  <si>
+    <t>LARISST SCRUB SPONGE</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
     <t>20131331</t>
   </si>
   <si>
     <t>AIRPRO A/F DAVD 10ML</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
     <t>20131332</t>
   </si>
   <si>
@@ -782,6 +788,18 @@
   </si>
   <si>
     <t>IDM SEDOTAN KRTS 20S</t>
+  </si>
+  <si>
+    <t>20142026</t>
+  </si>
+  <si>
+    <t>IDM SENDOK PLSTK 10S</t>
+  </si>
+  <si>
+    <t>20142027</t>
+  </si>
+  <si>
+    <t>IDM GARPU PLSTK 10S</t>
   </si>
   <si>
     <t>20111707</t>
@@ -1600,7 +1618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F182"/>
+  <dimension ref="A1:F185"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2461,10 +2479,10 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>99</v>
@@ -2504,18 +2522,18 @@
         <v>34</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2527,7 +2545,7 @@
         <v>10</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2544,10 +2562,10 @@
         <v>34</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2567,7 +2585,7 @@
         <v>29</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2584,10 +2602,10 @@
         <v>34</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>19</v>
+        <v>106</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2624,7 +2642,7 @@
         <v>34</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>19</v>
@@ -2644,7 +2662,7 @@
         <v>34</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>19</v>
@@ -2684,18 +2702,18 @@
         <v>34</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>123</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -2707,7 +2725,7 @@
         <v>22</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2724,10 +2742,10 @@
         <v>34</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2764,18 +2782,18 @@
         <v>34</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -2787,7 +2805,7 @@
         <v>58</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2804,10 +2822,10 @@
         <v>34</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>19</v>
+        <v>134</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2841,10 +2859,10 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>19</v>
@@ -2867,7 +2885,7 @@
         <v>4</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>104</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2884,10 +2902,10 @@
         <v>22</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>19</v>
+        <v>106</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2904,7 +2922,7 @@
         <v>22</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>19</v>
@@ -2924,7 +2942,7 @@
         <v>22</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>19</v>
@@ -2944,7 +2962,7 @@
         <v>22</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>19</v>
@@ -2964,7 +2982,7 @@
         <v>22</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>19</v>
@@ -2984,7 +3002,7 @@
         <v>22</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>19</v>
@@ -3004,7 +3022,7 @@
         <v>22</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>19</v>
@@ -3024,7 +3042,7 @@
         <v>22</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>19</v>
@@ -3044,10 +3062,10 @@
         <v>22</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>132</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3064,10 +3082,10 @@
         <v>22</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -3084,30 +3102,30 @@
         <v>22</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>165</v>
+        <v>66</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>19</v>
+        <v>134</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="C75" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E75" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C75" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F75" s="1" t="s">
-        <v>104</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3124,10 +3142,10 @@
         <v>39</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3144,10 +3162,10 @@
         <v>39</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3164,10 +3182,10 @@
         <v>39</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3184,10 +3202,10 @@
         <v>39</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3204,10 +3222,10 @@
         <v>39</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3224,10 +3242,10 @@
         <v>39</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3241,13 +3259,13 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3267,7 +3285,7 @@
         <v>4</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3284,10 +3302,10 @@
         <v>58</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3304,10 +3322,10 @@
         <v>58</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3324,18 +3342,18 @@
         <v>58</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>190</v>
+        <v>99</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>192</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -3344,10 +3362,10 @@
         <v>58</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3364,10 +3382,10 @@
         <v>58</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>99</v>
+        <v>192</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3381,13 +3399,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3407,7 +3425,7 @@
         <v>4</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3427,7 +3445,7 @@
         <v>4</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3444,10 +3462,10 @@
         <v>63</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3467,7 +3485,7 @@
         <v>10</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3484,10 +3502,10 @@
         <v>63</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3507,7 +3525,7 @@
         <v>29</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3524,10 +3542,10 @@
         <v>63</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3547,7 +3565,7 @@
         <v>15</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3567,7 +3585,7 @@
         <v>15</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3584,10 +3602,10 @@
         <v>63</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3607,7 +3625,7 @@
         <v>18</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3627,15 +3645,15 @@
         <v>18</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>221</v>
+        <v>106</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>223</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -3644,10 +3662,10 @@
         <v>63</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>104</v>
+        <v>223</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3664,18 +3682,18 @@
         <v>63</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>174</v>
+        <v>226</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>175</v>
+        <v>227</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
@@ -3687,15 +3705,15 @@
         <v>22</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>227</v>
+        <v>177</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -3704,10 +3722,10 @@
         <v>63</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3727,7 +3745,7 @@
         <v>39</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3744,10 +3762,10 @@
         <v>63</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3767,15 +3785,15 @@
         <v>58</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>234</v>
+        <v>106</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>236</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
@@ -3784,10 +3802,10 @@
         <v>63</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>104</v>
+        <v>236</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3807,7 +3825,7 @@
         <v>63</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3824,10 +3842,10 @@
         <v>63</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3844,10 +3862,10 @@
         <v>63</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>165</v>
+        <v>66</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3861,13 +3879,13 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>5</v>
+        <v>125</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3884,7 +3902,7 @@
         <v>66</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3904,7 +3922,7 @@
         <v>66</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3924,7 +3942,7 @@
         <v>66</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3944,7 +3962,7 @@
         <v>66</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3964,7 +3982,7 @@
         <v>66</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3984,7 +4002,7 @@
         <v>66</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -4001,13 +4019,13 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>165</v>
+        <v>66</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>234</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4021,10 +4039,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>165</v>
+        <v>66</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>99</v>
@@ -4041,13 +4059,13 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>165</v>
+        <v>66</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>234</v>
+        <v>99</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4061,13 +4079,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4081,13 +4099,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>234</v>
+        <v>99</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4101,13 +4119,13 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>99</v>
+        <v>236</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4121,13 +4139,13 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>19</v>
+        <v>236</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4141,13 +4159,13 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>99</v>
+        <v>236</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -4161,13 +4179,13 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4181,13 +4199,13 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4201,13 +4219,13 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4221,13 +4239,13 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4241,10 +4259,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4261,10 +4279,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>285</v>
+        <v>167</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4272,62 +4290,62 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>285</v>
+        <v>167</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>285</v>
+        <v>167</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>285</v>
-      </c>
       <c r="E136" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4341,10 +4359,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>19</v>
@@ -4361,10 +4379,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>19</v>
@@ -4381,10 +4399,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>19</v>
@@ -4401,13 +4419,13 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4421,10 +4439,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>19</v>
@@ -4441,10 +4459,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>19</v>
@@ -4461,10 +4479,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4472,59 +4490,59 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>308</v>
-      </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>310</v>
-      </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B146" s="1" t="s">
+      <c r="C146" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="C146" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="E146" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4541,10 +4559,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4561,13 +4579,13 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4581,13 +4599,13 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4601,13 +4619,13 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -4621,10 +4639,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>19</v>
@@ -4641,10 +4659,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>19</v>
@@ -4661,10 +4679,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>19</v>
@@ -4681,10 +4699,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>19</v>
@@ -4701,13 +4719,13 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>285</v>
+        <v>63</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>234</v>
+        <v>19</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4721,13 +4739,13 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>306</v>
+        <v>66</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4741,50 +4759,50 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>335</v>
+        <v>312</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>29</v>
+        <v>167</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>335</v>
+        <v>312</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>15</v>
+        <v>291</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>5</v>
+        <v>236</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>339</v>
-      </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>335</v>
+        <v>312</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>18</v>
+        <v>312</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4792,22 +4810,22 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B160" s="1" t="s">
+      <c r="C160" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="C160" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="E160" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -4821,13 +4839,13 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4841,13 +4859,13 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -4861,13 +4879,13 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -4881,10 +4899,10 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>19</v>
@@ -4901,10 +4919,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>19</v>
@@ -4921,13 +4939,13 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -4941,10 +4959,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>285</v>
+        <v>63</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>19</v>
@@ -4961,10 +4979,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>306</v>
+        <v>66</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>19</v>
@@ -4981,10 +4999,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>360</v>
+        <v>167</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>19</v>
@@ -4992,59 +5010,59 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>335</v>
+        <v>291</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>364</v>
-      </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>365</v>
+        <v>312</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E172" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>368</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>19</v>
@@ -5052,19 +5070,19 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>371</v>
+        <v>341</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5072,19 +5090,19 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5092,39 +5110,39 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5132,79 +5150,79 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>19</v>
@@ -5212,19 +5230,19 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>19</v>
@@ -5232,21 +5250,81 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A183" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="B182" s="1" t="s">
+      <c r="B183" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="C182" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="E182" s="1" t="s">
+      <c r="C183" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E183" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="F182" s="1" t="s">
+      <c r="F183" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A184" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A185" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="F185" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/HNM03S.xlsx
+++ b/HNM03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="404">
   <si>
     <t/>
   </si>
@@ -79,51 +79,51 @@
     <t>IDM CLING WRAP 30X30</t>
   </si>
   <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>10014035</t>
+  </si>
+  <si>
+    <t>BAGUS SK.LANTAI20920</t>
+  </si>
+  <si>
+    <t>10014036</t>
+  </si>
+  <si>
+    <t>BAGUS SKT.BAJU 20930</t>
+  </si>
+  <si>
+    <t>20039156</t>
+  </si>
+  <si>
+    <t>IDM J/HJN DISP DWSA</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20140873</t>
+  </si>
+  <si>
+    <t>IDM JAS HJ.DISP STLN</t>
+  </si>
+  <si>
+    <t>20071123</t>
+  </si>
+  <si>
+    <t>IDM JAS HUJAN SETLN</t>
+  </si>
+  <si>
+    <t>20090053</t>
+  </si>
+  <si>
+    <t>BAGUS KAIN LAP SBGNA</t>
+  </si>
+  <si>
     <t>7</t>
   </si>
   <si>
-    <t>10014035</t>
-  </si>
-  <si>
-    <t>BAGUS SK.LANTAI20920</t>
-  </si>
-  <si>
-    <t>10014036</t>
-  </si>
-  <si>
-    <t>BAGUS SKT.BAJU 20930</t>
-  </si>
-  <si>
-    <t>20039156</t>
-  </si>
-  <si>
-    <t>IDM J/HJN DISP DWSA</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20140873</t>
-  </si>
-  <si>
-    <t>IDM JAS HJ.DISP STLN</t>
-  </si>
-  <si>
-    <t>20071123</t>
-  </si>
-  <si>
-    <t>IDM JAS HUJAN SETLN</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20090053</t>
-  </si>
-  <si>
-    <t>BAGUS KAIN LAP SBGNA</t>
-  </si>
-  <si>
     <t>20038032</t>
   </si>
   <si>
@@ -250,18 +250,27 @@
     <t>NXCARE BBL SHWR PUFF</t>
   </si>
   <si>
-    <t>20089952</t>
-  </si>
-  <si>
-    <t>IDM PLS.SMPH H/B20'S</t>
-  </si>
-  <si>
     <t>20140686</t>
   </si>
   <si>
     <t>SB SPONS &amp; STNLS</t>
   </si>
   <si>
+    <t>20142226</t>
+  </si>
+  <si>
+    <t>IDM KTG SMPH 44X60CM</t>
+  </si>
+  <si>
+    <t>,(E-1B)</t>
+  </si>
+  <si>
+    <t>20142274</t>
+  </si>
+  <si>
+    <t>IDM ADHESIVE HOOKS 3</t>
+  </si>
+  <si>
     <t>20044863</t>
   </si>
   <si>
@@ -764,18 +773,6 @@
   </si>
   <si>
     <t>IDM PIRING KRTS 20'S</t>
-  </si>
-  <si>
-    <t>20055209</t>
-  </si>
-  <si>
-    <t>IDM SNDOK PLSTK 10'S</t>
-  </si>
-  <si>
-    <t>20055211</t>
-  </si>
-  <si>
-    <t>IDM GARPU PLSTK 10'S</t>
   </si>
   <si>
     <t>20043413</t>
@@ -1618,7 +1615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F185"/>
+  <dimension ref="A1:F184"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1882,7 +1879,7 @@
         <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -1890,10 +1887,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1902,7 +1899,7 @@
         <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>19</v>
@@ -2042,7 +2039,7 @@
         <v>29</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>19</v>
@@ -2062,7 +2059,7 @@
         <v>29</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>19</v>
@@ -2282,7 +2279,7 @@
         <v>15</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>19</v>
@@ -2302,10 +2299,10 @@
         <v>15</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2322,38 +2319,38 @@
         <v>15</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>19</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -2362,7 +2359,7 @@
         <v>18</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -2370,10 +2367,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -2382,18 +2379,18 @@
         <v>18</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -2402,7 +2399,7 @@
         <v>18</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>19</v>
@@ -2410,10 +2407,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2422,7 +2419,7 @@
         <v>18</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>19</v>
@@ -2430,10 +2427,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2445,15 +2442,15 @@
         <v>22</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -2462,7 +2459,7 @@
         <v>18</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -2470,10 +2467,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -2482,10 +2479,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>99</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2499,53 +2496,53 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2559,87 +2556,87 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>19</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>15</v>
@@ -2650,19 +2647,19 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>19</v>
@@ -2670,19 +2667,19 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>19</v>
@@ -2690,19 +2687,19 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>19</v>
@@ -2710,22 +2707,22 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>125</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2739,73 +2736,73 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F57" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>134</v>
+        <v>102</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2819,47 +2816,47 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>63</v>
@@ -2870,10 +2867,10 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
@@ -2882,7 +2879,7 @@
         <v>22</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>19</v>
@@ -2890,59 +2887,59 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>106</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>19</v>
+        <v>109</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>19</v>
@@ -2950,19 +2947,19 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>19</v>
@@ -2970,19 +2967,19 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>19</v>
@@ -2990,19 +2987,19 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>19</v>
@@ -3010,16 +3007,16 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>22</v>
@@ -3030,19 +3027,19 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>19</v>
@@ -3050,19 +3047,19 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>19</v>
@@ -3070,62 +3067,62 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>134</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>167</v>
+        <v>66</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>19</v>
+        <v>137</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3139,21 +3136,21 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>4</v>
+        <v>170</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>106</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -3162,18 +3159,18 @@
         <v>39</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
@@ -3182,18 +3179,18 @@
         <v>39</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
@@ -3202,18 +3199,18 @@
         <v>39</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -3222,18 +3219,18 @@
         <v>39</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -3242,18 +3239,18 @@
         <v>39</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
@@ -3265,35 +3262,35 @@
         <v>22</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
@@ -3305,15 +3302,15 @@
         <v>4</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
@@ -3322,18 +3319,18 @@
         <v>58</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
@@ -3342,18 +3339,18 @@
         <v>58</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -3362,10 +3359,10 @@
         <v>58</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>192</v>
+        <v>102</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3382,18 +3379,18 @@
         <v>58</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3402,38 +3399,38 @@
         <v>58</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>99</v>
+        <v>195</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3445,15 +3442,15 @@
         <v>4</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -3465,15 +3462,15 @@
         <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3482,18 +3479,18 @@
         <v>63</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3505,15 +3502,15 @@
         <v>10</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3522,18 +3519,18 @@
         <v>63</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3545,15 +3542,15 @@
         <v>29</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3562,18 +3559,18 @@
         <v>63</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3585,15 +3582,15 @@
         <v>15</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -3605,15 +3602,15 @@
         <v>15</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3622,18 +3619,18 @@
         <v>63</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -3645,15 +3642,15 @@
         <v>18</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -3665,7 +3662,7 @@
         <v>18</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>223</v>
+        <v>109</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3682,18 +3679,18 @@
         <v>63</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>106</v>
+        <v>226</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
@@ -3705,15 +3702,15 @@
         <v>22</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>176</v>
+        <v>229</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>177</v>
+        <v>230</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -3722,18 +3719,18 @@
         <v>63</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>228</v>
+        <v>179</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>229</v>
+        <v>180</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
@@ -3742,18 +3739,18 @@
         <v>63</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
@@ -3765,15 +3762,15 @@
         <v>39</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -3782,18 +3779,18 @@
         <v>63</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
@@ -3805,7 +3802,7 @@
         <v>58</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>236</v>
+        <v>109</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3822,18 +3819,18 @@
         <v>63</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>106</v>
+        <v>239</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
@@ -3845,15 +3842,15 @@
         <v>63</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
@@ -3862,18 +3859,18 @@
         <v>63</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
@@ -3882,38 +3879,38 @@
         <v>63</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>167</v>
+        <v>66</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>4</v>
+        <v>170</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>5</v>
+        <v>128</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
@@ -3922,7 +3919,7 @@
         <v>66</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3930,10 +3927,10 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
@@ -3942,7 +3939,7 @@
         <v>66</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3950,10 +3947,10 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
@@ -3962,7 +3959,7 @@
         <v>66</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3970,10 +3967,10 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -3982,7 +3979,7 @@
         <v>66</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3990,10 +3987,10 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
@@ -4002,7 +3999,7 @@
         <v>66</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -4010,10 +4007,10 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
@@ -4022,18 +4019,18 @@
         <v>66</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>5</v>
+        <v>102</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
@@ -4045,224 +4042,224 @@
         <v>58</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>66</v>
+        <v>170</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>99</v>
+        <v>239</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>236</v>
+        <v>102</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>99</v>
+        <v>239</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>236</v>
+        <v>102</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4270,19 +4267,19 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4290,19 +4287,19 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4310,19 +4307,19 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>167</v>
+        <v>290</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4330,39 +4327,39 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B136" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>291</v>
-      </c>
       <c r="E136" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>19</v>
@@ -4370,19 +4367,19 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>19</v>
@@ -4390,19 +4387,19 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>19</v>
@@ -4410,19 +4407,19 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>19</v>
@@ -4430,19 +4427,19 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>19</v>
@@ -4450,59 +4447,59 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>19</v>
@@ -4510,39 +4507,39 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B146" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="C146" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>312</v>
-      </c>
       <c r="E146" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4550,19 +4547,19 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4570,19 +4567,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4590,19 +4587,19 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4610,39 +4607,39 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>19</v>
@@ -4650,19 +4647,19 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>19</v>
@@ -4670,19 +4667,19 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>19</v>
@@ -4690,19 +4687,19 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>19</v>
@@ -4710,19 +4707,19 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>19</v>
@@ -4730,19 +4727,19 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>66</v>
+        <v>170</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>19</v>
@@ -4750,59 +4747,59 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>167</v>
+        <v>290</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>19</v>
+        <v>239</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>236</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>312</v>
+        <v>340</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>312</v>
+        <v>29</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4810,19 +4807,19 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B160" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="C160" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>341</v>
-      </c>
       <c r="E160" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -4830,19 +4827,19 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -4850,39 +4847,39 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>19</v>
@@ -4890,19 +4887,19 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>19</v>
@@ -4910,59 +4907,59 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>19</v>
@@ -4970,19 +4967,19 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>66</v>
+        <v>170</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>19</v>
@@ -4990,19 +4987,19 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>167</v>
+        <v>290</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>19</v>
@@ -5010,19 +5007,19 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>19</v>
@@ -5030,19 +5027,19 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>312</v>
+        <v>365</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>19</v>
@@ -5050,39 +5047,39 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>366</v>
+        <v>340</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>341</v>
+        <v>370</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5090,59 +5087,59 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5150,19 +5147,19 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5170,19 +5167,19 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5190,39 +5187,39 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>19</v>
@@ -5230,19 +5227,19 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>19</v>
@@ -5250,19 +5247,19 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>19</v>
@@ -5270,19 +5267,19 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>19</v>
@@ -5290,41 +5287,21 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A185" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="E185" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="F185" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/HNM03S.xlsx
+++ b/HNM03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="403">
   <si>
     <t/>
   </si>
@@ -262,7 +262,7 @@
     <t>IDM KTG SMPH 44X60CM</t>
   </si>
   <si>
-    <t>,(E-1B)</t>
+    <t>PT,(E-1B)</t>
   </si>
   <si>
     <t>20142274</t>
@@ -728,9 +728,6 @@
   </si>
   <si>
     <t>IDM CAT FOOD TUNA 80</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
   </si>
   <si>
     <t>20126940</t>
@@ -3822,15 +3819,15 @@
         <v>58</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>239</v>
+        <v>83</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>241</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
@@ -3847,10 +3844,10 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>243</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
@@ -3867,10 +3864,10 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>245</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
@@ -3887,10 +3884,10 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>247</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
@@ -3907,10 +3904,10 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>249</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
@@ -3927,10 +3924,10 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>251</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
@@ -3947,10 +3944,10 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>253</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
@@ -3967,10 +3964,10 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>255</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -3987,10 +3984,10 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>257</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
@@ -4007,10 +4004,10 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>258</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>259</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
@@ -4027,10 +4024,10 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>261</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
@@ -4047,10 +4044,10 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>263</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
@@ -4062,15 +4059,15 @@
         <v>4</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>239</v>
+        <v>83</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>264</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>265</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
@@ -4087,10 +4084,10 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>267</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
@@ -4102,15 +4099,15 @@
         <v>10</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>239</v>
+        <v>83</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>269</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
@@ -4122,15 +4119,15 @@
         <v>10</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>239</v>
+        <v>83</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>271</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
@@ -4142,15 +4139,15 @@
         <v>29</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>239</v>
+        <v>83</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>273</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
@@ -4167,10 +4164,10 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>275</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
@@ -4187,10 +4184,10 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>277</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
@@ -4207,10 +4204,10 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>279</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
@@ -4227,10 +4224,10 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>281</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
@@ -4247,10 +4244,10 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>283</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
@@ -4267,10 +4264,10 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>285</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
@@ -4287,10 +4284,10 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>287</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
@@ -4307,16 +4304,16 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="C135" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>290</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>4</v>
@@ -4327,16 +4324,16 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>292</v>
-      </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>10</v>
@@ -4347,16 +4344,16 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>294</v>
-      </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>29</v>
@@ -4367,16 +4364,16 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>296</v>
-      </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>15</v>
@@ -4387,16 +4384,16 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>298</v>
-      </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>18</v>
@@ -4407,16 +4404,16 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>22</v>
@@ -4427,16 +4424,16 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>302</v>
-      </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>36</v>
@@ -4447,16 +4444,16 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>39</v>
@@ -4467,16 +4464,16 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>58</v>
@@ -4487,16 +4484,16 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>308</v>
-      </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>63</v>
@@ -4507,16 +4504,16 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B145" s="1" t="s">
+      <c r="C145" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>310</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>311</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>4</v>
@@ -4527,16 +4524,16 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>10</v>
@@ -4547,16 +4544,16 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>315</v>
-      </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>29</v>
@@ -4567,16 +4564,16 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>15</v>
@@ -4587,16 +4584,16 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>18</v>
@@ -4607,16 +4604,16 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>321</v>
-      </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>22</v>
@@ -4627,16 +4624,16 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>36</v>
@@ -4647,16 +4644,16 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>325</v>
-      </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>39</v>
@@ -4667,16 +4664,16 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>327</v>
-      </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>58</v>
@@ -4687,16 +4684,16 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>329</v>
-      </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>63</v>
@@ -4707,16 +4704,16 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>331</v>
-      </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>66</v>
@@ -4727,16 +4724,16 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>333</v>
-      </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>170</v>
@@ -4747,39 +4744,39 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>239</v>
+        <v>83</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4787,16 +4784,16 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B159" s="1" t="s">
+      <c r="C159" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>340</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>29</v>
@@ -4807,16 +4804,16 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>342</v>
-      </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>15</v>
@@ -4827,16 +4824,16 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>18</v>
@@ -4847,16 +4844,16 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>22</v>
@@ -4867,16 +4864,16 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>36</v>
@@ -4887,16 +4884,16 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>39</v>
@@ -4907,16 +4904,16 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>352</v>
-      </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>58</v>
@@ -4927,16 +4924,16 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>354</v>
-      </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>63</v>
@@ -4947,16 +4944,16 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>356</v>
-      </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>66</v>
@@ -4967,16 +4964,16 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>358</v>
-      </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>170</v>
@@ -4987,19 +4984,19 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B169" s="1" t="s">
-        <v>360</v>
-      </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>19</v>
@@ -5007,19 +5004,19 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>19</v>
@@ -5027,19 +5024,19 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B171" s="1" t="s">
+      <c r="C171" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E171" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="E171" s="1" t="s">
-        <v>365</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>19</v>
@@ -5047,19 +5044,19 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>367</v>
-      </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5067,19 +5064,19 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E173" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="E173" s="1" t="s">
-        <v>370</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5087,19 +5084,19 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B174" s="1" t="s">
+      <c r="C174" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E174" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="E174" s="1" t="s">
-        <v>373</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>19</v>
@@ -5107,19 +5104,19 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="B175" s="1" t="s">
+      <c r="C175" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E175" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="C175" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="E175" s="1" t="s">
-        <v>376</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5127,19 +5124,19 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="B176" s="1" t="s">
+      <c r="C176" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E176" s="1" t="s">
         <v>378</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="E176" s="1" t="s">
-        <v>379</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5147,19 +5144,19 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B177" s="1" t="s">
+      <c r="C177" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E177" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="E177" s="1" t="s">
-        <v>382</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5167,19 +5164,19 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E178" s="1" t="s">
         <v>384</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="E178" s="1" t="s">
-        <v>385</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5187,19 +5184,19 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B179" s="1" t="s">
+      <c r="C179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E179" s="1" t="s">
         <v>387</v>
-      </c>
-      <c r="C179" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="E179" s="1" t="s">
-        <v>388</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>19</v>
@@ -5207,19 +5204,19 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="B180" s="1" t="s">
+      <c r="C180" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E180" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="C180" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="E180" s="1" t="s">
-        <v>391</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>19</v>
@@ -5227,19 +5224,19 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="C181" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E181" s="1" t="s">
         <v>393</v>
-      </c>
-      <c r="C181" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="E181" s="1" t="s">
-        <v>394</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>19</v>
@@ -5247,19 +5244,19 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B182" s="1" t="s">
+      <c r="C182" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E182" s="1" t="s">
         <v>396</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>397</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>19</v>
@@ -5267,19 +5264,19 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B183" s="1" t="s">
+      <c r="C183" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E183" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>400</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>19</v>
@@ -5287,19 +5284,19 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B184" s="1" t="s">
+      <c r="C184" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E184" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="E184" s="1" t="s">
-        <v>403</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>

--- a/HNM03S.xlsx
+++ b/HNM03S.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="396">
   <si>
     <t/>
   </si>
   <si>
-    <t>20118913</t>
-  </si>
-  <si>
-    <t>IDM TAS RMH LNGK SDG</t>
+    <t>20074710</t>
+  </si>
+  <si>
+    <t>IDM KESET HANDUK</t>
   </si>
   <si>
     <t>HNM03S</t>
@@ -31,46 +31,100 @@
     <t>PT</t>
   </si>
   <si>
-    <t>20125992</t>
-  </si>
-  <si>
-    <t>IDM TAS RMH LNKG KTR</t>
-  </si>
-  <si>
-    <t>20107742</t>
-  </si>
-  <si>
-    <t>IDM TAS RMH LNGK KCL</t>
+    <t>20118382</t>
+  </si>
+  <si>
+    <t>AVENUE KSET HNDK PRM</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20122043</t>
-  </si>
-  <si>
-    <t>IDM TAS RMH LNGK BSR</t>
-  </si>
-  <si>
-    <t>20074710</t>
-  </si>
-  <si>
-    <t>IDM KESET HANDUK</t>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20071123</t>
+  </si>
+  <si>
+    <t>IDM JAS HUJAN SETLN</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20140873</t>
+  </si>
+  <si>
+    <t>IDM JAS HJ.DISP STLN</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20118382</t>
-  </si>
-  <si>
-    <t>AVENUE KSET HNDK PRM</t>
+    <t>20039156</t>
+  </si>
+  <si>
+    <t>IDM J/HJN DISP DWSA</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>10014035</t>
+  </si>
+  <si>
+    <t>BAGUS SK.LANTAI20920</t>
+  </si>
+  <si>
+    <t>10014036</t>
+  </si>
+  <si>
+    <t>BAGUS SKT.BAJU 20930</t>
+  </si>
+  <si>
+    <t>10006200</t>
+  </si>
+  <si>
+    <t>BAGUS SHOE BRSH 3354</t>
+  </si>
+  <si>
+    <t>20090053</t>
+  </si>
+  <si>
+    <t>BAGUS KAIN LAP SBGNA</t>
+  </si>
+  <si>
+    <t>20030983</t>
+  </si>
+  <si>
+    <t>IDM SERBET HANDUK</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>RT</t>
+    <t>20038032</t>
+  </si>
+  <si>
+    <t>IDM KAIN LAP PEL</t>
+  </si>
+  <si>
+    <t>20085916</t>
+  </si>
+  <si>
+    <t>IDM FOOD SVR 2'S 750</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20121395</t>
+  </si>
+  <si>
+    <t>KIIP RCTANGLR 10S 1L</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
   <si>
     <t>20092994</t>
@@ -79,58 +133,7 @@
     <t>IDM CLING WRAP 30X30</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>10014035</t>
-  </si>
-  <si>
-    <t>BAGUS SK.LANTAI20920</t>
-  </si>
-  <si>
-    <t>10014036</t>
-  </si>
-  <si>
-    <t>BAGUS SKT.BAJU 20930</t>
-  </si>
-  <si>
-    <t>20039156</t>
-  </si>
-  <si>
-    <t>IDM J/HJN DISP DWSA</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20140873</t>
-  </si>
-  <si>
-    <t>IDM JAS HJ.DISP STLN</t>
-  </si>
-  <si>
-    <t>20071123</t>
-  </si>
-  <si>
-    <t>IDM JAS HUJAN SETLN</t>
-  </si>
-  <si>
-    <t>20090053</t>
-  </si>
-  <si>
-    <t>BAGUS KAIN LAP SBGNA</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20038032</t>
-  </si>
-  <si>
-    <t>IDM KAIN LAP PEL</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>9</t>
   </si>
   <si>
     <t>20062464</t>
@@ -145,18 +148,6 @@
     <t>IDM TUSUK GIGI 200'S</t>
   </si>
   <si>
-    <t>20085916</t>
-  </si>
-  <si>
-    <t>IDM FOOD SVR 2'S 750</t>
-  </si>
-  <si>
-    <t>20121395</t>
-  </si>
-  <si>
-    <t>KIIP RCTANGLR 10S 1L</t>
-  </si>
-  <si>
     <t>20026412</t>
   </si>
   <si>
@@ -181,88 +172,622 @@
     <t>IDM LILIN PUTIH 8'S</t>
   </si>
   <si>
+    <t>20072837</t>
+  </si>
+  <si>
+    <t>IDM LILIN ULTAH 12'S</t>
+  </si>
+  <si>
+    <t>20142226</t>
+  </si>
+  <si>
+    <t>IDM KTG SMPH 44X60CM</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20084539</t>
+  </si>
+  <si>
+    <t>KRSBOW GLOVE LATEX</t>
+  </si>
+  <si>
+    <t>20128556</t>
+  </si>
+  <si>
+    <t>IDM PLSTK KLIP 15X10</t>
+  </si>
+  <si>
+    <t>20128557</t>
+  </si>
+  <si>
+    <t>IDM PLSTK KLIP 25X16</t>
+  </si>
+  <si>
     <t>20082114</t>
   </si>
   <si>
     <t>IDM PLSTK HDPE 15X30</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>20082115</t>
   </si>
   <si>
     <t>IDM PLSTK HDPE 20X35</t>
   </si>
   <si>
-    <t>20030983</t>
-  </si>
-  <si>
-    <t>IDM SERBET HANDUK</t>
+    <t>20086810</t>
+  </si>
+  <si>
+    <t>IDM LAP SERBAGUNA</t>
+  </si>
+  <si>
+    <t>20098808</t>
+  </si>
+  <si>
+    <t>BAGUS SRG TGN PLS100</t>
+  </si>
+  <si>
+    <t>20141993</t>
+  </si>
+  <si>
+    <t>LARISST SCRUB SPONGE</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20044863</t>
+  </si>
+  <si>
+    <t>IDM SABUT STNLSS 2'S</t>
+  </si>
+  <si>
+    <t>20139062</t>
+  </si>
+  <si>
+    <t>LARISST SABUT CUCI2S</t>
+  </si>
+  <si>
+    <t>10003530</t>
+  </si>
+  <si>
+    <t>S/B TOUGH CLN SCRB</t>
+  </si>
+  <si>
+    <t>20053561</t>
+  </si>
+  <si>
+    <t>SB EASY CLN SCRB SPG</t>
+  </si>
+  <si>
+    <t>20113117</t>
+  </si>
+  <si>
+    <t>SC.BRITE SBT.JRG M60</t>
+  </si>
+  <si>
+    <t>20129462</t>
+  </si>
+  <si>
+    <t>IDM SPGE MND LG PUFF</t>
+  </si>
+  <si>
+    <t>20033662</t>
+  </si>
+  <si>
+    <t>IDM SPONGE MANDI PCK</t>
+  </si>
+  <si>
+    <t>20133214</t>
+  </si>
+  <si>
+    <t>NXCARE BBL SHWR PUFF</t>
+  </si>
+  <si>
+    <t>20131332</t>
+  </si>
+  <si>
+    <t>AIRPRO A/F CHNL 10ML</t>
+  </si>
+  <si>
+    <t>20080042</t>
+  </si>
+  <si>
+    <t>BYFRSH HANG'N GO CRV</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20101038</t>
+  </si>
+  <si>
+    <t>BYFRSH HANG'N GO LIM</t>
+  </si>
+  <si>
+    <t>20048540</t>
+  </si>
+  <si>
+    <t>STELLA DAILY/F ORG/B</t>
+  </si>
+  <si>
+    <t>20048539</t>
+  </si>
+  <si>
+    <t>STELLA DAILY/F RED/K</t>
+  </si>
+  <si>
+    <t>20130343</t>
+  </si>
+  <si>
+    <t>CLFORNIA A/F STRWBRY</t>
+  </si>
+  <si>
+    <t>20138691</t>
+  </si>
+  <si>
+    <t>STELLA CAR HANG JASM</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20138690</t>
+  </si>
+  <si>
+    <t>STELLA CAR HANG AQUA</t>
+  </si>
+  <si>
+    <t>20052689</t>
+  </si>
+  <si>
+    <t>AMBI PUR SKY/BR 2ML</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20111567</t>
+  </si>
+  <si>
+    <t>KAGUMI D.SCNT COFFEE</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>10006200</t>
-  </si>
-  <si>
-    <t>BAGUS SHOE BRSH 3354</t>
+    <t>20111568</t>
+  </si>
+  <si>
+    <t>KAGUMI D.SCNT T.MNGO</t>
   </si>
   <si>
     <t>11</t>
   </si>
   <si>
-    <t>20128556</t>
-  </si>
-  <si>
-    <t>IDM PLSTK KLIP 15X10</t>
-  </si>
-  <si>
-    <t>20128557</t>
-  </si>
-  <si>
-    <t>IDM PLSTK KLIP 25X16</t>
-  </si>
-  <si>
-    <t>20072837</t>
-  </si>
-  <si>
-    <t>IDM LILIN ULTAH 12'S</t>
-  </si>
-  <si>
-    <t>20086810</t>
-  </si>
-  <si>
-    <t>IDM LAP SERBAGUNA</t>
-  </si>
-  <si>
-    <t>20098808</t>
-  </si>
-  <si>
-    <t>BAGUS SRG TGN PLS100</t>
-  </si>
-  <si>
-    <t>20133214</t>
-  </si>
-  <si>
-    <t>NXCARE BBL SHWR PUFF</t>
-  </si>
-  <si>
-    <t>20140686</t>
-  </si>
-  <si>
-    <t>SB SPONS &amp; STNLS</t>
-  </si>
-  <si>
-    <t>20142226</t>
-  </si>
-  <si>
-    <t>IDM KTG SMPH 44X60CM</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
+    <t>20132836</t>
+  </si>
+  <si>
+    <t>AIRPRO A/F OCEAN 9ML</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>10005473</t>
+  </si>
+  <si>
+    <t>KIT WASH&amp;GLOW PCH720</t>
+  </si>
+  <si>
+    <t>20130417</t>
+  </si>
+  <si>
+    <t>GLO WSH&amp;SHN SHMPO700</t>
+  </si>
+  <si>
+    <t>10028422</t>
+  </si>
+  <si>
+    <t>KIT WIPER FLD PCH400</t>
+  </si>
+  <si>
+    <t>20001713</t>
+  </si>
+  <si>
+    <t>KIT BLACK MGC GEL180</t>
+  </si>
+  <si>
+    <t>20109707</t>
+  </si>
+  <si>
+    <t>KIT WATERLESS BTL500</t>
+  </si>
+  <si>
+    <t>20090436</t>
+  </si>
+  <si>
+    <t>KIT DETAILER SPRY200</t>
+  </si>
+  <si>
+    <t>20121376</t>
+  </si>
+  <si>
+    <t>KIT MOTOR B TO B 115</t>
+  </si>
+  <si>
+    <t>20013832</t>
+  </si>
+  <si>
+    <t>KIT MOTOR MLTGUNA100</t>
+  </si>
+  <si>
+    <t>20037676</t>
+  </si>
+  <si>
+    <t>KIT MTR CHN.LUBE 110</t>
+  </si>
+  <si>
+    <t>10016210</t>
+  </si>
+  <si>
+    <t>AMBI PUR VAN.BQT 7.5</t>
+  </si>
+  <si>
+    <t>10016209</t>
+  </si>
+  <si>
+    <t>AMBI/P C/FR.AQUA 7.5</t>
+  </si>
+  <si>
+    <t>20016897</t>
+  </si>
+  <si>
+    <t>GLADE CAR FRSH APL70</t>
+  </si>
+  <si>
+    <t>20135615</t>
+  </si>
+  <si>
+    <t>CAT CHOIZE+T&amp;S 1.2KG</t>
+  </si>
+  <si>
+    <t>20140135</t>
+  </si>
+  <si>
+    <t>CUTIES CATZ TUNA 500</t>
+  </si>
+  <si>
+    <t>20106045</t>
+  </si>
+  <si>
+    <t>CAT CHOIZE+ T&amp;S 500G</t>
+  </si>
+  <si>
+    <t>20126381</t>
+  </si>
+  <si>
+    <t>RLR TYPE PWRFUL MOP</t>
+  </si>
+  <si>
+    <t>20064471</t>
+  </si>
+  <si>
+    <t>WHISKAS TUNA 480G</t>
+  </si>
+  <si>
+    <t>20088717</t>
+  </si>
+  <si>
+    <t>ME-O CAT FD TUNA 200</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20064072</t>
+  </si>
+  <si>
+    <t>ME-O CAT FD TUNA 450</t>
+  </si>
+  <si>
+    <t>20119165</t>
+  </si>
+  <si>
+    <t>CAT CHZ+ KTN T&amp;S 450</t>
+  </si>
+  <si>
+    <t>20128689</t>
+  </si>
+  <si>
+    <t>CAT CHZE+ TN&amp;MRL 500</t>
+  </si>
+  <si>
+    <t>20134229</t>
+  </si>
+  <si>
+    <t>ME-O TUNA IN JLY 400</t>
+  </si>
+  <si>
+    <t>20134226</t>
+  </si>
+  <si>
+    <t>ME-O TUNA IN JLLY400</t>
+  </si>
+  <si>
+    <t>20128697</t>
+  </si>
+  <si>
+    <t>LFE CAT OCN FS TN400</t>
+  </si>
+  <si>
+    <t>20031235</t>
+  </si>
+  <si>
+    <t>WHISKAS JR CF TUN 80</t>
+  </si>
+  <si>
+    <t>20090536</t>
+  </si>
+  <si>
+    <t>WHISKAS.JR OCEAN 50G</t>
+  </si>
+  <si>
+    <t>20113921</t>
+  </si>
+  <si>
+    <t>ME-O KITTEN TUNA 80G</t>
+  </si>
+  <si>
+    <t>20031238</t>
+  </si>
+  <si>
+    <t>WHISKAS JR MCKRL 80</t>
+  </si>
+  <si>
+    <t>20117628</t>
+  </si>
+  <si>
+    <t>WHKAS T/M TNA KNKM70</t>
+  </si>
+  <si>
+    <t>20121362</t>
+  </si>
+  <si>
+    <t>ME-O OTAK2 WF 80G</t>
+  </si>
+  <si>
+    <t>RT,(E-9B)</t>
+  </si>
+  <si>
+    <t>20096777</t>
+  </si>
+  <si>
+    <t>WHISKAS OCEAN FSH 80</t>
+  </si>
+  <si>
+    <t>20117626</t>
+  </si>
+  <si>
+    <t>WHKAS T/M CHK TUNA70</t>
+  </si>
+  <si>
+    <t>20121357</t>
+  </si>
+  <si>
+    <t>ME-O OCEAN FISH 80G</t>
+  </si>
+  <si>
+    <t>20031232</t>
+  </si>
+  <si>
+    <t>WHISKAS CF TUNA 80</t>
+  </si>
+  <si>
+    <t>20113920</t>
+  </si>
+  <si>
+    <t>ME-O TUNA IN JLY 80G</t>
+  </si>
+  <si>
+    <t>20140134</t>
+  </si>
+  <si>
+    <t>CUTIES CATZ TUNA 75G</t>
+  </si>
+  <si>
+    <t>20031233</t>
+  </si>
+  <si>
+    <t>WHISKAS CF MAC&amp;SAL80</t>
+  </si>
+  <si>
+    <t>20121808</t>
+  </si>
+  <si>
+    <t>ME-O OTAK2 WF&amp;CS 80G</t>
+  </si>
+  <si>
+    <t>20128696</t>
+  </si>
+  <si>
+    <t>LIFE CAT KTEN TUNA85</t>
+  </si>
+  <si>
+    <t>20102393</t>
+  </si>
+  <si>
+    <t>ME-O KTN OCN.FISH 50</t>
+  </si>
+  <si>
+    <t>20126940</t>
+  </si>
+  <si>
+    <t>K/B CAT FD SLMON 120</t>
+  </si>
+  <si>
+    <t>20135980</t>
+  </si>
+  <si>
+    <t>IDM CAT FOOD TUNA 80</t>
+  </si>
+  <si>
+    <t>20104599</t>
+  </si>
+  <si>
+    <t>ME-O CRM TRT SLMN 60</t>
+  </si>
+  <si>
+    <t>20128695</t>
+  </si>
+  <si>
+    <t>BIO CREAMY TUNA 4S</t>
+  </si>
+  <si>
+    <t>20135431</t>
+  </si>
+  <si>
+    <t>DELI CRMY TUNA 2X14G</t>
+  </si>
+  <si>
+    <t>20104595</t>
+  </si>
+  <si>
+    <t>ME-O CRM CHKN&amp;LVR 60</t>
+  </si>
+  <si>
+    <t>20134232</t>
+  </si>
+  <si>
+    <t>SH CRMY TREATS 4X15G</t>
+  </si>
+  <si>
+    <t>20135432</t>
+  </si>
+  <si>
+    <t>DELI CRM TN&amp;SLMN2X14</t>
+  </si>
+  <si>
+    <t>20098413</t>
+  </si>
+  <si>
+    <t>IDM PIRING KRTS 10'S</t>
+  </si>
+  <si>
+    <t>20098414</t>
+  </si>
+  <si>
+    <t>IDM MNGKOK KRTS 10'S</t>
+  </si>
+  <si>
+    <t>20043412</t>
+  </si>
+  <si>
+    <t>IDM PIRING KRTS 20'S</t>
+  </si>
+  <si>
+    <t>20142026</t>
+  </si>
+  <si>
+    <t>IDM SENDOK PLSTK 10S</t>
+  </si>
+  <si>
+    <t>20142027</t>
+  </si>
+  <si>
+    <t>IDM GARPU PLSTK 10S</t>
+  </si>
+  <si>
+    <t>20043413</t>
+  </si>
+  <si>
+    <t>IDM GELAS KRTS 20'S</t>
+  </si>
+  <si>
+    <t>20096978</t>
+  </si>
+  <si>
+    <t>IDM SEDOTAN KRTS 20S</t>
+  </si>
+  <si>
+    <t>20131278</t>
+  </si>
+  <si>
+    <t>IDM DUCKBILL PTIH 4S</t>
+  </si>
+  <si>
+    <t>20131301</t>
+  </si>
+  <si>
+    <t>IDM DUCKBILL HTAM 4S</t>
+  </si>
+  <si>
+    <t>20111707</t>
+  </si>
+  <si>
+    <t>IDM MASKER 4D PTH 4S</t>
+  </si>
+  <si>
+    <t>20115472</t>
+  </si>
+  <si>
+    <t>IDM MASK 4D HTM 4'S</t>
+  </si>
+  <si>
+    <t>20117862</t>
+  </si>
+  <si>
+    <t>IDM MASKER PCK 5'S</t>
+  </si>
+  <si>
+    <t>20120506</t>
+  </si>
+  <si>
+    <t>IDM MASKER HIJAB 5'S</t>
+  </si>
+  <si>
+    <t>20085748</t>
+  </si>
+  <si>
+    <t>NXCARE CRBN MASK 2'S</t>
+  </si>
+  <si>
+    <t>20118218</t>
+  </si>
+  <si>
+    <t>IDM MSK SLIM HTM 5S</t>
+  </si>
+  <si>
+    <t>20071626</t>
+  </si>
+  <si>
+    <t>XANDER GEMBOK 50MM</t>
+  </si>
+  <si>
+    <t>20142764</t>
+  </si>
+  <si>
+    <t>IDM MSKR SLIM PTH 5S</t>
+  </si>
+  <si>
+    <t>20097529</t>
+  </si>
+  <si>
+    <t>KRSBOW PADLOCK 21031</t>
+  </si>
+  <si>
+    <t>20101650</t>
+  </si>
+  <si>
+    <t>B6.ESS BAG HLDR HOOK</t>
+  </si>
+  <si>
+    <t>20038033</t>
+  </si>
+  <si>
+    <t>IDM TALI RAFIA</t>
   </si>
   <si>
     <t>20142274</t>
@@ -271,55 +796,163 @@
     <t>IDM ADHESIVE HOOKS 3</t>
   </si>
   <si>
-    <t>20044863</t>
-  </si>
-  <si>
-    <t>IDM SABUT STNLSS 2'S</t>
-  </si>
-  <si>
-    <t>20139062</t>
-  </si>
-  <si>
-    <t>LARISST SABUT CUCI2S</t>
-  </si>
-  <si>
-    <t>10003530</t>
-  </si>
-  <si>
-    <t>S/B TOUGH CLN SCRB</t>
-  </si>
-  <si>
-    <t>20053561</t>
-  </si>
-  <si>
-    <t>SB EASY CLN SCRB SPG</t>
-  </si>
-  <si>
-    <t>20113117</t>
-  </si>
-  <si>
-    <t>SC.BRITE SBT.JRG M60</t>
-  </si>
-  <si>
-    <t>20129462</t>
-  </si>
-  <si>
-    <t>IDM SPGE MND LG PUFF</t>
-  </si>
-  <si>
-    <t>20033662</t>
-  </si>
-  <si>
-    <t>IDM SPONGE MANDI PCK</t>
-  </si>
-  <si>
-    <t>20141993</t>
-  </si>
-  <si>
-    <t>LARISST SCRUB SPONGE</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
+    <t>20126285</t>
+  </si>
+  <si>
+    <t>KRSBW HS/CLM B.FLY2S</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20135301</t>
+  </si>
+  <si>
+    <t>SCOTCH MOUNT TAPE</t>
+  </si>
+  <si>
+    <t>20126993</t>
+  </si>
+  <si>
+    <t>KNMSTER SEAL TAPE 2S</t>
+  </si>
+  <si>
+    <t>20026187</t>
+  </si>
+  <si>
+    <t>KEN/M RING SEAL GAS</t>
+  </si>
+  <si>
+    <t>20011831</t>
+  </si>
+  <si>
+    <t>KEN/M REG+MTR KM-911</t>
+  </si>
+  <si>
+    <t>20125690</t>
+  </si>
+  <si>
+    <t>IDM PNGKAT KABEL 50S</t>
+  </si>
+  <si>
+    <t>20115861</t>
+  </si>
+  <si>
+    <t>SHKAKU CBL TIES 100S</t>
+  </si>
+  <si>
+    <t>20078869</t>
+  </si>
+  <si>
+    <t>KRSBOW V.TESTER 250V</t>
+  </si>
+  <si>
+    <t>20032449</t>
+  </si>
+  <si>
+    <t>KEN/M STEKER L009</t>
+  </si>
+  <si>
+    <t>20080374</t>
+  </si>
+  <si>
+    <t>KEN/M ADPT USB S0203</t>
+  </si>
+  <si>
+    <t>20134307</t>
+  </si>
+  <si>
+    <t>PHILIPS LED E27 13WT</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20123181</t>
+  </si>
+  <si>
+    <t>PHILIPS LED E27 11WT</t>
+  </si>
+  <si>
+    <t>20055290</t>
+  </si>
+  <si>
+    <t>PHILIPS LED C/DYL 8W</t>
+  </si>
+  <si>
+    <t>20046933</t>
+  </si>
+  <si>
+    <t>PHILIP LED C/DYL 6W</t>
+  </si>
+  <si>
+    <t>20052902</t>
+  </si>
+  <si>
+    <t>PHILIPS LED C/DYL 4W</t>
+  </si>
+  <si>
+    <t>20101464</t>
+  </si>
+  <si>
+    <t>HANNOCHS C/D SNC 12W</t>
+  </si>
+  <si>
+    <t>20101463</t>
+  </si>
+  <si>
+    <t>HANNOCHS C/D SNC 5W</t>
+  </si>
+  <si>
+    <t>20094959</t>
+  </si>
+  <si>
+    <t>IN-LITE LED BOX 9W</t>
+  </si>
+  <si>
+    <t>20134457</t>
+  </si>
+  <si>
+    <t>IN-LITE LED BOX 15W</t>
+  </si>
+  <si>
+    <t>20060010</t>
+  </si>
+  <si>
+    <t>LGHTSPRO LMP LED12WT</t>
+  </si>
+  <si>
+    <t>10003074</t>
+  </si>
+  <si>
+    <t>ZIPPO LGHTR FLD 133</t>
+  </si>
+  <si>
+    <t>20084542</t>
+  </si>
+  <si>
+    <t>MGCOOLS CHAIN LB 300</t>
+  </si>
+  <si>
+    <t>20130008</t>
+  </si>
+  <si>
+    <t>LARISST TOKAI GAS235</t>
+  </si>
+  <si>
+    <t>20066636</t>
+  </si>
+  <si>
+    <t>BRIGHT GAS KLG 220G</t>
+  </si>
+  <si>
+    <t>20034850</t>
+  </si>
+  <si>
+    <t>INDOMARET ALAT PEL</t>
+  </si>
+  <si>
+    <t>16</t>
   </si>
   <si>
     <t>20131331</t>
@@ -328,25 +961,16 @@
     <t>AIRPRO A/F DAVD 10ML</t>
   </si>
   <si>
-    <t>20131332</t>
-  </si>
-  <si>
-    <t>AIRPRO A/F CHNL 10ML</t>
-  </si>
-  <si>
-    <t>20080042</t>
-  </si>
-  <si>
-    <t>BYFRSH HANG'N GO CRV</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20101038</t>
-  </si>
-  <si>
-    <t>BYFRSH HANG'N GO LIM</t>
+    <t>20124786</t>
+  </si>
+  <si>
+    <t>BAYFRESH CPUCCINO 70</t>
+  </si>
+  <si>
+    <t>20076488</t>
+  </si>
+  <si>
+    <t>IDM SAPU LIDI TABAH</t>
   </si>
   <si>
     <t>20117814</t>
@@ -355,16 +979,22 @@
     <t>BYFRSH H 'N GO SKR/B</t>
   </si>
   <si>
+    <t>20071449</t>
+  </si>
+  <si>
+    <t>IDM PAYUNG PJG WRNA</t>
+  </si>
+  <si>
     <t>20117815</t>
   </si>
   <si>
     <t>BYFRSH H 'N GO D/ICE</t>
   </si>
   <si>
-    <t>20048539</t>
-  </si>
-  <si>
-    <t>STELLA DAILY/F RED/K</t>
+    <t>20126374</t>
+  </si>
+  <si>
+    <t>TOILETBRUSH GRAY WHT</t>
   </si>
   <si>
     <t>20055262</t>
@@ -373,10 +1003,22 @@
     <t>STELLA DAILY/F DRM 7</t>
   </si>
   <si>
-    <t>20048540</t>
-  </si>
-  <si>
-    <t>STELLA DAILY/F ORG/B</t>
+    <t>20035266</t>
+  </si>
+  <si>
+    <t>INDOMARET PEL REFILL</t>
+  </si>
+  <si>
+    <t>20052690</t>
+  </si>
+  <si>
+    <t>AMBI PUR LVDR/C 2ML</t>
+  </si>
+  <si>
+    <t>20032453</t>
+  </si>
+  <si>
+    <t>KEN/M STP KNTK F1-4</t>
   </si>
   <si>
     <t>20130339</t>
@@ -385,31 +1027,10 @@
     <t>CLFORNIA A/F NEWPORT</t>
   </si>
   <si>
-    <t>20130343</t>
-  </si>
-  <si>
-    <t>CLFORNIA A/F STRWBRY</t>
-  </si>
-  <si>
-    <t>20138690</t>
-  </si>
-  <si>
-    <t>STELLA CAR HANG AQUA</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20138691</t>
-  </si>
-  <si>
-    <t>STELLA CAR HANG JASM</t>
-  </si>
-  <si>
-    <t>20132836</t>
-  </si>
-  <si>
-    <t>AIRPRO A/F OCEAN 9ML</t>
+    <t>20126378</t>
+  </si>
+  <si>
+    <t>2PCS DETACBLE BROOM</t>
   </si>
   <si>
     <t>20138849</t>
@@ -418,631 +1039,7 @@
     <t>AIRPRO ESS FRUITY 9</t>
   </si>
   <si>
-    <t>20052689</t>
-  </si>
-  <si>
-    <t>AMBI PUR SKY/BR 2ML</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20052690</t>
-  </si>
-  <si>
-    <t>AMBI PUR LVDR/C 2ML</t>
-  </si>
-  <si>
-    <t>20111567</t>
-  </si>
-  <si>
-    <t>KAGUMI D.SCNT COFFEE</t>
-  </si>
-  <si>
-    <t>20111568</t>
-  </si>
-  <si>
-    <t>KAGUMI D.SCNT T.MNGO</t>
-  </si>
-  <si>
-    <t>10005473</t>
-  </si>
-  <si>
-    <t>KIT WASH&amp;GLOW PCH720</t>
-  </si>
-  <si>
-    <t>20124786</t>
-  </si>
-  <si>
-    <t>BAYFRESH CPUCCINO 70</t>
-  </si>
-  <si>
-    <t>20130417</t>
-  </si>
-  <si>
-    <t>GLO WSH&amp;SHN SHMPO700</t>
-  </si>
-  <si>
-    <t>10028422</t>
-  </si>
-  <si>
-    <t>KIT WIPER FLD PCH400</t>
-  </si>
-  <si>
-    <t>20001713</t>
-  </si>
-  <si>
-    <t>KIT BLACK MGC GEL180</t>
-  </si>
-  <si>
-    <t>20109707</t>
-  </si>
-  <si>
-    <t>KIT WATERLESS BTL500</t>
-  </si>
-  <si>
-    <t>20090436</t>
-  </si>
-  <si>
-    <t>KIT DETAILER SPRY200</t>
-  </si>
-  <si>
-    <t>20121376</t>
-  </si>
-  <si>
-    <t>KIT MOTOR B TO B 115</t>
-  </si>
-  <si>
-    <t>20013832</t>
-  </si>
-  <si>
-    <t>KIT MOTOR MLTGUNA100</t>
-  </si>
-  <si>
-    <t>20037676</t>
-  </si>
-  <si>
-    <t>KIT MTR CHN.LUBE 110</t>
-  </si>
-  <si>
-    <t>10016210</t>
-  </si>
-  <si>
-    <t>AMBI PUR VAN.BQT 7.5</t>
-  </si>
-  <si>
-    <t>10016209</t>
-  </si>
-  <si>
-    <t>AMBI/P C/FR.AQUA 7.5</t>
-  </si>
-  <si>
-    <t>20016897</t>
-  </si>
-  <si>
-    <t>GLADE CAR FRSH APL70</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20135615</t>
-  </si>
-  <si>
-    <t>CAT CHOIZE+T&amp;S 1.2KG</t>
-  </si>
-  <si>
-    <t>20106045</t>
-  </si>
-  <si>
-    <t>CAT CHOIZE+ T&amp;S 500G</t>
-  </si>
-  <si>
-    <t>20119165</t>
-  </si>
-  <si>
-    <t>CAT CHZ+ KTN T&amp;S 450</t>
-  </si>
-  <si>
-    <t>20128689</t>
-  </si>
-  <si>
-    <t>CAT CHZE+ TN&amp;MRL 500</t>
-  </si>
-  <si>
-    <t>20134229</t>
-  </si>
-  <si>
-    <t>ME-O TUNA IN JLY 400</t>
-  </si>
-  <si>
-    <t>20134226</t>
-  </si>
-  <si>
-    <t>ME-O TUNA IN JLLY400</t>
-  </si>
-  <si>
-    <t>20128697</t>
-  </si>
-  <si>
-    <t>LFE CAT OCN FS TN400</t>
-  </si>
-  <si>
-    <t>20031233</t>
-  </si>
-  <si>
-    <t>WHISKAS CF MAC&amp;SAL80</t>
-  </si>
-  <si>
-    <t>20141219</t>
-  </si>
-  <si>
-    <t>WHSKAS JR TUNA 180G</t>
-  </si>
-  <si>
-    <t>20064471</t>
-  </si>
-  <si>
-    <t>WHISKAS TUNA 480G</t>
-  </si>
-  <si>
-    <t>20141220</t>
-  </si>
-  <si>
-    <t>WHSKAS ADLT TUNA 200</t>
-  </si>
-  <si>
-    <t>20088717</t>
-  </si>
-  <si>
-    <t>ME-O CAT FD TUNA 200</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20064072</t>
-  </si>
-  <si>
-    <t>ME-O CAT FD TUNA 450</t>
-  </si>
-  <si>
-    <t>20140135</t>
-  </si>
-  <si>
-    <t>CUTIES CATZ TUNA 500</t>
-  </si>
-  <si>
-    <t>20031235</t>
-  </si>
-  <si>
-    <t>WHISKAS JR CF TUN 80</t>
-  </si>
-  <si>
-    <t>20031238</t>
-  </si>
-  <si>
-    <t>WHISKAS JR MCKRL 80</t>
-  </si>
-  <si>
-    <t>20090536</t>
-  </si>
-  <si>
-    <t>WHISKAS.JR OCEAN 50G</t>
-  </si>
-  <si>
-    <t>20117626</t>
-  </si>
-  <si>
-    <t>WHKAS T/M CHK TUNA70</t>
-  </si>
-  <si>
-    <t>20117628</t>
-  </si>
-  <si>
-    <t>WHKAS T/M TNA KNKM70</t>
-  </si>
-  <si>
-    <t>20031232</t>
-  </si>
-  <si>
-    <t>WHISKAS CF TUNA 80</t>
-  </si>
-  <si>
-    <t>20096777</t>
-  </si>
-  <si>
-    <t>WHISKAS OCEAN FSH 80</t>
-  </si>
-  <si>
-    <t>20113921</t>
-  </si>
-  <si>
-    <t>ME-O KITTEN TUNA 80G</t>
-  </si>
-  <si>
-    <t>20121357</t>
-  </si>
-  <si>
-    <t>ME-O OCEAN FISH 80G</t>
-  </si>
-  <si>
-    <t>20121808</t>
-  </si>
-  <si>
-    <t>ME-O OTAK2 WF&amp;CS 80G</t>
-  </si>
-  <si>
-    <t>20104599</t>
-  </si>
-  <si>
-    <t>ME-O CRM TRT SLMN 60</t>
-  </si>
-  <si>
-    <t>20113920</t>
-  </si>
-  <si>
-    <t>ME-O TUNA IN JLY 80G</t>
-  </si>
-  <si>
-    <t>20121362</t>
-  </si>
-  <si>
-    <t>ME-O OTAK2 WF 80G</t>
-  </si>
-  <si>
-    <t>RT,(E-9B)</t>
-  </si>
-  <si>
-    <t>20104595</t>
-  </si>
-  <si>
-    <t>ME-O CRM CHKN&amp;LVR 60</t>
-  </si>
-  <si>
-    <t>20102393</t>
-  </si>
-  <si>
-    <t>ME-O KTN OCN.FISH 50</t>
-  </si>
-  <si>
-    <t>20128695</t>
-  </si>
-  <si>
-    <t>BIO CREAMY TUNA 4S</t>
-  </si>
-  <si>
-    <t>20135432</t>
-  </si>
-  <si>
-    <t>DELI CRM TN&amp;SLMN2X14</t>
-  </si>
-  <si>
-    <t>20135431</t>
-  </si>
-  <si>
-    <t>DELI CRMY TUNA 2X14G</t>
-  </si>
-  <si>
-    <t>20135980</t>
-  </si>
-  <si>
-    <t>IDM CAT FOOD TUNA 80</t>
-  </si>
-  <si>
-    <t>20126940</t>
-  </si>
-  <si>
-    <t>K/B CAT FD SLMON 120</t>
-  </si>
-  <si>
-    <t>20128696</t>
-  </si>
-  <si>
-    <t>LIFE CAT KTEN TUNA85</t>
-  </si>
-  <si>
-    <t>20140134</t>
-  </si>
-  <si>
-    <t>CUTIES CATZ TUNA 75G</t>
-  </si>
-  <si>
-    <t>20134232</t>
-  </si>
-  <si>
-    <t>SH CRMY TREATS 4X15G</t>
-  </si>
-  <si>
-    <t>20098414</t>
-  </si>
-  <si>
-    <t>IDM MNGKOK KRTS 10'S</t>
-  </si>
-  <si>
-    <t>20098413</t>
-  </si>
-  <si>
-    <t>IDM PIRING KRTS 10'S</t>
-  </si>
-  <si>
-    <t>20043412</t>
-  </si>
-  <si>
-    <t>IDM PIRING KRTS 20'S</t>
-  </si>
-  <si>
-    <t>20043413</t>
-  </si>
-  <si>
-    <t>IDM GELAS KRTS 20'S</t>
-  </si>
-  <si>
-    <t>20096978</t>
-  </si>
-  <si>
-    <t>IDM SEDOTAN KRTS 20S</t>
-  </si>
-  <si>
-    <t>20142026</t>
-  </si>
-  <si>
-    <t>IDM SENDOK PLSTK 10S</t>
-  </si>
-  <si>
-    <t>20142027</t>
-  </si>
-  <si>
-    <t>IDM GARPU PLSTK 10S</t>
-  </si>
-  <si>
-    <t>20111707</t>
-  </si>
-  <si>
-    <t>IDM MASKER 4D PTH 4S</t>
-  </si>
-  <si>
-    <t>20131278</t>
-  </si>
-  <si>
-    <t>IDM DUCKBILL PTIH 4S</t>
-  </si>
-  <si>
-    <t>20115472</t>
-  </si>
-  <si>
-    <t>IDM MASK 4D HTM 4'S</t>
-  </si>
-  <si>
-    <t>20120506</t>
-  </si>
-  <si>
-    <t>IDM MASKER HIJAB 5'S</t>
-  </si>
-  <si>
-    <t>20117862</t>
-  </si>
-  <si>
-    <t>IDM MASKER PCK 5'S</t>
-  </si>
-  <si>
-    <t>20131301</t>
-  </si>
-  <si>
-    <t>IDM DUCKBILL HTAM 4S</t>
-  </si>
-  <si>
-    <t>20085748</t>
-  </si>
-  <si>
-    <t>NXCARE CRBN MASK 2'S</t>
-  </si>
-  <si>
-    <t>20118218</t>
-  </si>
-  <si>
-    <t>IDM MSK SLIM HTM 5S</t>
-  </si>
-  <si>
-    <t>20071626</t>
-  </si>
-  <si>
-    <t>XANDER GEMBOK 50MM</t>
-  </si>
-  <si>
-    <t>20097529</t>
-  </si>
-  <si>
-    <t>KRSBOW PADLOCK 21031</t>
-  </si>
-  <si>
-    <t>20084539</t>
-  </si>
-  <si>
-    <t>KRSBOW GLOVE LATEX</t>
-  </si>
-  <si>
-    <t>20101650</t>
-  </si>
-  <si>
-    <t>B6.ESS BAG HLDR HOOK</t>
-  </si>
-  <si>
-    <t>20038033</t>
-  </si>
-  <si>
-    <t>IDM TALI RAFIA</t>
-  </si>
-  <si>
-    <t>20126285</t>
-  </si>
-  <si>
-    <t>KRSBW HS/CLM B.FLY2S</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20135301</t>
-  </si>
-  <si>
-    <t>SCOTCH MOUNT TAPE</t>
-  </si>
-  <si>
-    <t>20126993</t>
-  </si>
-  <si>
-    <t>KNMSTER SEAL TAPE 2S</t>
-  </si>
-  <si>
-    <t>20115861</t>
-  </si>
-  <si>
-    <t>SHKAKU CBL TIES 100S</t>
-  </si>
-  <si>
-    <t>20026187</t>
-  </si>
-  <si>
-    <t>KEN/M RING SEAL GAS</t>
-  </si>
-  <si>
-    <t>20011831</t>
-  </si>
-  <si>
-    <t>KEN/M REG+MTR KM-911</t>
-  </si>
-  <si>
-    <t>20125690</t>
-  </si>
-  <si>
-    <t>IDM PNGKAT KABEL 50S</t>
-  </si>
-  <si>
-    <t>20078869</t>
-  </si>
-  <si>
-    <t>KRSBOW V.TESTER 250V</t>
-  </si>
-  <si>
-    <t>20032449</t>
-  </si>
-  <si>
-    <t>KEN/M STEKER L009</t>
-  </si>
-  <si>
-    <t>20080374</t>
-  </si>
-  <si>
-    <t>KEN/M ADPT USB S0203</t>
-  </si>
-  <si>
-    <t>20134307</t>
-  </si>
-  <si>
-    <t>PHILIPS LED E27 13WT</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20123181</t>
-  </si>
-  <si>
-    <t>PHILIPS LED E27 11WT</t>
-  </si>
-  <si>
-    <t>20055290</t>
-  </si>
-  <si>
-    <t>PHILIPS LED C/DYL 8W</t>
-  </si>
-  <si>
-    <t>20046933</t>
-  </si>
-  <si>
-    <t>PHILIP LED C/DYL 6W</t>
-  </si>
-  <si>
-    <t>20052902</t>
-  </si>
-  <si>
-    <t>PHILIPS LED C/DYL 4W</t>
-  </si>
-  <si>
-    <t>20101464</t>
-  </si>
-  <si>
-    <t>HANNOCHS C/D SNC 12W</t>
-  </si>
-  <si>
-    <t>20101463</t>
-  </si>
-  <si>
-    <t>HANNOCHS C/D SNC 5W</t>
-  </si>
-  <si>
-    <t>20094959</t>
-  </si>
-  <si>
-    <t>IN-LITE LED BOX 9W</t>
-  </si>
-  <si>
-    <t>20134457</t>
-  </si>
-  <si>
-    <t>IN-LITE LED BOX 15W</t>
-  </si>
-  <si>
-    <t>20060010</t>
-  </si>
-  <si>
-    <t>LGHTSPRO LMP LED12WT</t>
-  </si>
-  <si>
-    <t>10003074</t>
-  </si>
-  <si>
-    <t>ZIPPO LGHTR FLD 133</t>
-  </si>
-  <si>
-    <t>20084542</t>
-  </si>
-  <si>
-    <t>MGCOOLS CHAIN LB 300</t>
-  </si>
-  <si>
-    <t>20130008</t>
-  </si>
-  <si>
-    <t>LARISST TOKAI GAS235</t>
-  </si>
-  <si>
-    <t>20066636</t>
-  </si>
-  <si>
-    <t>BRIGHT GAS KLG 220G</t>
-  </si>
-  <si>
-    <t>20076488</t>
-  </si>
-  <si>
-    <t>IDM SAPU LIDI TABAH</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20034850</t>
-  </si>
-  <si>
-    <t>INDOMARET ALAT PEL</t>
-  </si>
-  <si>
-    <t>20071449</t>
-  </si>
-  <si>
-    <t>IDM PAYUNG PJG WRNA</t>
+    <t>15</t>
   </si>
   <si>
     <t>20126370</t>
@@ -1051,28 +1048,40 @@
     <t>COOGER MOP CMO4609</t>
   </si>
   <si>
-    <t>20126378</t>
-  </si>
-  <si>
-    <t>2PCS DETACBLE BROOM</t>
-  </si>
-  <si>
-    <t>20126374</t>
-  </si>
-  <si>
-    <t>TOILETBRUSH GRAY WHT</t>
-  </si>
-  <si>
-    <t>20035266</t>
-  </si>
-  <si>
-    <t>INDOMARET PEL REFILL</t>
-  </si>
-  <si>
-    <t>20032453</t>
-  </si>
-  <si>
-    <t>KEN/M STP KNTK F1-4</t>
+    <t>20037222</t>
+  </si>
+  <si>
+    <t>KEN/M RKT NYM+SNTR B</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20011832</t>
+  </si>
+  <si>
+    <t>KEN/M REG+MTR PROTCN</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20053613</t>
+  </si>
+  <si>
+    <t>IDM TALI TAMBANG 6MM</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20074350</t>
+  </si>
+  <si>
+    <t>IDM PAYUNG LPT TIGA</t>
+  </si>
+  <si>
+    <t>20</t>
   </si>
   <si>
     <t>20026807</t>
@@ -1081,16 +1090,25 @@
     <t>KEN/M OBENG SET MN6</t>
   </si>
   <si>
+    <t>21</t>
+  </si>
+  <si>
     <t>20060033</t>
   </si>
   <si>
     <t>KEN/M WTR FLTR DAIYU</t>
   </si>
   <si>
-    <t>20011832</t>
-  </si>
-  <si>
-    <t>KEN/M REG+MTR PROTCN</t>
+    <t>22</t>
+  </si>
+  <si>
+    <t>10016469</t>
+  </si>
+  <si>
+    <t>KEN/M GAS LIGHTER</t>
+  </si>
+  <si>
+    <t>23</t>
   </si>
   <si>
     <t>20121040</t>
@@ -1099,37 +1117,43 @@
     <t>KEN/M KRAN PLSTK PTH</t>
   </si>
   <si>
-    <t>10016469</t>
-  </si>
-  <si>
-    <t>KEN/M GAS LIGHTER</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20053613</t>
-  </si>
-  <si>
-    <t>IDM TALI TAMBANG 6MM</t>
-  </si>
-  <si>
-    <t>20074350</t>
-  </si>
-  <si>
-    <t>IDM PAYUNG LPT TIGA</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20037222</t>
-  </si>
-  <si>
-    <t>KEN/M RKT NYM+SNTR B</t>
-  </si>
-  <si>
-    <t>20</t>
+    <t>24</t>
+  </si>
+  <si>
+    <t>20139712</t>
+  </si>
+  <si>
+    <t>IDM SANDAL JPT KRT38</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>20072320</t>
+  </si>
+  <si>
+    <t>IDM SNDAL PRIA 39-40</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>20072322</t>
+  </si>
+  <si>
+    <t>IDM SNDAL PRIA 41-42</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>20093212</t>
+  </si>
+  <si>
+    <t>IDM SANDAL JPT KRT42</t>
+  </si>
+  <si>
+    <t>28</t>
   </si>
   <si>
     <t>20093211</t>
@@ -1138,34 +1162,16 @@
     <t>IDM SANDAL JPT KRT40</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>20072320</t>
-  </si>
-  <si>
-    <t>IDM SNDAL PRIA 39-40</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>20072322</t>
-  </si>
-  <si>
-    <t>IDM SNDAL PRIA 41-42</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>20093212</t>
-  </si>
-  <si>
-    <t>IDM SANDAL JPT KRT42</t>
-  </si>
-  <si>
-    <t>25</t>
+    <t>29</t>
+  </si>
+  <si>
+    <t>20126380</t>
+  </si>
+  <si>
+    <t>30CLIP WINDPROF BSKT</t>
+  </si>
+  <si>
+    <t>30</t>
   </si>
   <si>
     <t>20118405</t>
@@ -1174,16 +1180,7 @@
     <t>CLARIS EMBER 12 TTP</t>
   </si>
   <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>20126380</t>
-  </si>
-  <si>
-    <t>30CLIP WINDPROF BSKT</t>
-  </si>
-  <si>
-    <t>27</t>
+    <t>31</t>
   </si>
   <si>
     <t>20127779</t>
@@ -1192,7 +1189,7 @@
     <t>COOGER WALL SOAP W+G</t>
   </si>
   <si>
-    <t>28</t>
+    <t>32</t>
   </si>
   <si>
     <t>20126372</t>
@@ -1201,25 +1198,7 @@
     <t>DISC MULTI TOOHBRUSH</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>20126381</t>
-  </si>
-  <si>
-    <t>RLR TYPE PWRFUL MOP</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>20139712</t>
-  </si>
-  <si>
-    <t>IDM SANDAL JPT KRT38</t>
-  </si>
-  <si>
-    <t>31</t>
+    <t>33</t>
   </si>
 </sst>
 </file>
@@ -1612,7 +1591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F184"/>
+  <dimension ref="A1:F177"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1676,18 +1655,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -1696,7 +1675,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>5</v>
@@ -1704,10 +1683,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -1716,7 +1695,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>5</v>
@@ -1724,10 +1703,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -1736,7 +1715,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>5</v>
@@ -1744,42 +1723,42 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1793,13 +1772,13 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1813,13 +1792,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1833,7 +1812,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>29</v>
@@ -1853,7 +1832,7 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>18</v>
@@ -1873,10 +1852,10 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -1884,56 +1863,56 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>4</v>
@@ -1944,19 +1923,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -1964,139 +1943,139 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F20" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>5</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -2104,19 +2083,19 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -2124,19 +2103,19 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -2153,21 +2132,21 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -2176,7 +2155,7 @@
         <v>15</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -2184,10 +2163,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -2196,18 +2175,18 @@
         <v>15</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -2216,30 +2195,30 @@
         <v>15</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2253,13 +2232,13 @@
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2273,13 +2252,13 @@
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2293,13 +2272,13 @@
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="F34" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2313,50 +2292,50 @@
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>83</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>83</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -2364,19 +2343,19 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -2384,30 +2363,30 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2416,18 +2395,18 @@
         <v>18</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2436,10 +2415,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2456,10 +2435,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>5</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2476,10 +2455,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2496,50 +2475,50 @@
         <v>18</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="C46" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2553,33 +2532,33 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="C48" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F48" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2593,1093 +2572,1093 @@
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>29</v>
+        <v>114</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>109</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>109</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>128</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>128</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>137</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>19</v>
+        <v>157</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B70" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F70" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>19</v>
+        <v>106</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>137</v>
+        <v>106</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>137</v>
+        <v>95</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>170</v>
+        <v>4</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>128</v>
+        <v>182</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>128</v>
+        <v>95</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>195</v>
+        <v>95</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>195</v>
+        <v>95</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>109</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>109</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>109</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>226</v>
+        <v>74</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3693,13 +3672,13 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3713,250 +3692,250 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>109</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>179</v>
+        <v>231</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>180</v>
+        <v>232</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>128</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>170</v>
+        <v>15</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>128</v>
+        <v>74</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>5</v>
+        <v>74</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3964,19 +3943,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3984,19 +3963,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -4004,239 +3983,239 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>66</v>
+        <v>263</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>102</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>170</v>
+        <v>263</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>83</v>
+        <v>9</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="E123" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>170</v>
+        <v>263</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>83</v>
+        <v>9</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>170</v>
+        <v>263</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>83</v>
+        <v>9</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>170</v>
+        <v>263</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>83</v>
+        <v>9</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>170</v>
+        <v>263</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>170</v>
+        <v>263</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>170</v>
+        <v>263</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>170</v>
+        <v>263</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>18</v>
+        <v>114</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>170</v>
+        <v>284</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -4244,19 +4223,19 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>170</v>
+        <v>284</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4264,19 +4243,19 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B133" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="E133" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4284,19 +4263,19 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>170</v>
+        <v>284</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4304,19 +4283,19 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4324,196 +4303,196 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>22</v>
+        <v>114</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>36</v>
+        <v>117</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>39</v>
+        <v>120</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>58</v>
+        <v>263</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>63</v>
+        <v>284</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>4</v>
@@ -4524,56 +4503,56 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>5</v>
+        <v>74</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>310</v>
-      </c>
       <c r="E147" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>5</v>
+        <v>95</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>15</v>
@@ -4584,479 +4563,479 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>5</v>
+        <v>95</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>289</v>
+        <v>263</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>83</v>
+        <v>9</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>310</v>
+        <v>284</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>339</v>
+        <v>313</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>29</v>
+        <v>342</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>5</v>
+        <v>74</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>339</v>
+        <v>313</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>15</v>
+        <v>313</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>339</v>
+        <v>313</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>18</v>
+        <v>347</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>339</v>
+        <v>313</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>22</v>
+        <v>350</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>339</v>
+        <v>313</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>36</v>
+        <v>353</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>339</v>
+        <v>313</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>39</v>
+        <v>356</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>339</v>
+        <v>313</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>58</v>
+        <v>359</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>339</v>
+        <v>313</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>63</v>
+        <v>362</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>339</v>
+        <v>313</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>66</v>
+        <v>365</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>339</v>
+        <v>313</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>170</v>
+        <v>368</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>339</v>
+        <v>313</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>289</v>
+        <v>371</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>339</v>
+        <v>313</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>310</v>
+        <v>374</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>339</v>
+        <v>313</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>364</v>
+        <v>377</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>339</v>
+        <v>313</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>339</v>
+        <v>380</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5064,19 +5043,19 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>339</v>
+        <v>313</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5084,222 +5063,82 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>339</v>
+        <v>313</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>339</v>
+        <v>313</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>339</v>
+        <v>313</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>339</v>
+        <v>313</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A178" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="E178" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="F178" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A179" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="C179" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="E179" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="F179" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A180" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="C180" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="E180" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="F180" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A181" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="B181" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="C181" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="E181" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="F181" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A182" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="F182" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A183" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="F183" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A184" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="B184" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="E184" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="F184" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/HNM03S.xlsx
+++ b/HNM03S.xlsx
@@ -289,7 +289,7 @@
     <t>20131332</t>
   </si>
   <si>
-    <t>AIRPRO A/F CHNL 10ML</t>
+    <t>AIRPRO A/F SKR LMI10</t>
   </si>
   <si>
     <t>20080042</t>
@@ -958,7 +958,7 @@
     <t>20131331</t>
   </si>
   <si>
-    <t>AIRPRO A/F DAVD 10ML</t>
+    <t>AIRPRO A/F CLWV TD10</t>
   </si>
   <si>
     <t>20124786</t>

--- a/HNM03S.xlsx
+++ b/HNM03S.xlsx
@@ -3918,7 +3918,7 @@
         <v>29</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">

--- a/HNM03S.xlsx
+++ b/HNM03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="390">
   <si>
     <t/>
   </si>
@@ -43,13 +43,22 @@
     <t>RT</t>
   </si>
   <si>
+    <t>20143373</t>
+  </si>
+  <si>
+    <t>IDM KSET HNDK PRMIUM</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>20071123</t>
   </si>
   <si>
     <t>IDM JAS HUJAN SETLN</t>
   </si>
   <si>
-    <t>3</t>
+    <t>4</t>
   </si>
   <si>
     <t>20140873</t>
@@ -58,7 +67,436 @@
     <t>IDM JAS HJ.DISP STLN</t>
   </si>
   <si>
-    <t>4</t>
+    <t>5</t>
+  </si>
+  <si>
+    <t>10014035</t>
+  </si>
+  <si>
+    <t>BAGUS SK.LANTAI20920</t>
+  </si>
+  <si>
+    <t>10014036</t>
+  </si>
+  <si>
+    <t>BAGUS SKT.BAJU 20930</t>
+  </si>
+  <si>
+    <t>10006200</t>
+  </si>
+  <si>
+    <t>BAGUS SHOE BRSH 3354</t>
+  </si>
+  <si>
+    <t>20090053</t>
+  </si>
+  <si>
+    <t>BAGUS KAIN LAP SBGNA</t>
+  </si>
+  <si>
+    <t>20030983</t>
+  </si>
+  <si>
+    <t>IDM SERBET HANDUK</t>
+  </si>
+  <si>
+    <t>20038032</t>
+  </si>
+  <si>
+    <t>IDM KAIN LAP PEL</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20085916</t>
+  </si>
+  <si>
+    <t>IDM FOOD SVR 2'S 750</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20121395</t>
+  </si>
+  <si>
+    <t>KIIP RCTANGLR 10S 1L</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20092994</t>
+  </si>
+  <si>
+    <t>IDM CLING WRAP 30X30</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20062464</t>
+  </si>
+  <si>
+    <t>IDM TSK GIGI TRAVEL</t>
+  </si>
+  <si>
+    <t>20038650</t>
+  </si>
+  <si>
+    <t>IDM TUSUK GIGI 200'S</t>
+  </si>
+  <si>
+    <t>20026412</t>
+  </si>
+  <si>
+    <t>INDOMARET LAP MOTOR</t>
+  </si>
+  <si>
+    <t>20026410</t>
+  </si>
+  <si>
+    <t>INDOMARET LAP MOBIL</t>
+  </si>
+  <si>
+    <t>20036334</t>
+  </si>
+  <si>
+    <t>KEN/M MTR WASH SPNG</t>
+  </si>
+  <si>
+    <t>20075589</t>
+  </si>
+  <si>
+    <t>IDM LILIN PUTIH 8'S</t>
+  </si>
+  <si>
+    <t>20072837</t>
+  </si>
+  <si>
+    <t>IDM LILIN ULTAH 12'S</t>
+  </si>
+  <si>
+    <t>20142226</t>
+  </si>
+  <si>
+    <t>IDM KTG SMPH 44X60CM</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20084539</t>
+  </si>
+  <si>
+    <t>KRSBOW GLOVE LATEX</t>
+  </si>
+  <si>
+    <t>20128556</t>
+  </si>
+  <si>
+    <t>IDM PLSTK KLIP 15X10</t>
+  </si>
+  <si>
+    <t>20128557</t>
+  </si>
+  <si>
+    <t>IDM PLSTK KLIP 25X16</t>
+  </si>
+  <si>
+    <t>20082114</t>
+  </si>
+  <si>
+    <t>IDM PLSTK HDPE 15X30</t>
+  </si>
+  <si>
+    <t>20082115</t>
+  </si>
+  <si>
+    <t>IDM PLSTK HDPE 20X35</t>
+  </si>
+  <si>
+    <t>20086810</t>
+  </si>
+  <si>
+    <t>IDM LAP SERBAGUNA</t>
+  </si>
+  <si>
+    <t>20098808</t>
+  </si>
+  <si>
+    <t>BAGUS SRG TGN PLS100</t>
+  </si>
+  <si>
+    <t>20141993</t>
+  </si>
+  <si>
+    <t>LARISST SCRUB SPONGE</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20044863</t>
+  </si>
+  <si>
+    <t>IDM SABUT STNLSS 2'S</t>
+  </si>
+  <si>
+    <t>20139062</t>
+  </si>
+  <si>
+    <t>LARISST SABUT CUCI2S</t>
+  </si>
+  <si>
+    <t>10003530</t>
+  </si>
+  <si>
+    <t>S/B TOUGH CLN SCRB</t>
+  </si>
+  <si>
+    <t>20053561</t>
+  </si>
+  <si>
+    <t>SB EASY CLN SCRB SPG</t>
+  </si>
+  <si>
+    <t>20113117</t>
+  </si>
+  <si>
+    <t>SC.BRITE SBT.JRG M60</t>
+  </si>
+  <si>
+    <t>20129462</t>
+  </si>
+  <si>
+    <t>IDM SPGE MND LG PUFF</t>
+  </si>
+  <si>
+    <t>20033662</t>
+  </si>
+  <si>
+    <t>IDM SPONGE MANDI PCK</t>
+  </si>
+  <si>
+    <t>20133214</t>
+  </si>
+  <si>
+    <t>NXCARE BBL SHWR PUFF</t>
+  </si>
+  <si>
+    <t>20131331</t>
+  </si>
+  <si>
+    <t>AIRPRO A/F CLWV TD10</t>
+  </si>
+  <si>
+    <t>20131332</t>
+  </si>
+  <si>
+    <t>AIRPRO A/F SKR LMI10</t>
+  </si>
+  <si>
+    <t>20080042</t>
+  </si>
+  <si>
+    <t>BYFRSH HANG'N GO CRV</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20117814</t>
+  </si>
+  <si>
+    <t>BYFRSH H 'N GO SKR/B</t>
+  </si>
+  <si>
+    <t>20101038</t>
+  </si>
+  <si>
+    <t>BYFRSH HANG'N GO LIM</t>
+  </si>
+  <si>
+    <t>20117815</t>
+  </si>
+  <si>
+    <t>BYFRSH H 'N GO D/ICE</t>
+  </si>
+  <si>
+    <t>20048540</t>
+  </si>
+  <si>
+    <t>STELLA DAILY/F ORG/B</t>
+  </si>
+  <si>
+    <t>20055262</t>
+  </si>
+  <si>
+    <t>STELLA DAILY/F DRM 7</t>
+  </si>
+  <si>
+    <t>20048539</t>
+  </si>
+  <si>
+    <t>STELLA DAILY/F RED/K</t>
+  </si>
+  <si>
+    <t>20052690</t>
+  </si>
+  <si>
+    <t>AMBI PUR LVDR/C 2ML</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20130339</t>
+  </si>
+  <si>
+    <t>CLFORNIA A/F NEWPORT</t>
+  </si>
+  <si>
+    <t>20130343</t>
+  </si>
+  <si>
+    <t>CLFORNIA A/F STRWBRY</t>
+  </si>
+  <si>
+    <t>20138691</t>
+  </si>
+  <si>
+    <t>STELLA CAR HANG JASM</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20138849</t>
+  </si>
+  <si>
+    <t>AIRPRO ESS FRUITY 9</t>
+  </si>
+  <si>
+    <t>20138690</t>
+  </si>
+  <si>
+    <t>STELLA CAR HANG AQUA</t>
+  </si>
+  <si>
+    <t>20052689</t>
+  </si>
+  <si>
+    <t>AMBI PUR SKY/BR 2ML</t>
+  </si>
+  <si>
+    <t>20111567</t>
+  </si>
+  <si>
+    <t>KAGUMI D.SCNT COFFEE</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20111568</t>
+  </si>
+  <si>
+    <t>KAGUMI D.SCNT T.MNGO</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20132836</t>
+  </si>
+  <si>
+    <t>AIRPRO A/F OCEAN 9ML</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>10005473</t>
+  </si>
+  <si>
+    <t>KIT WASH&amp;GLOW PCH720</t>
+  </si>
+  <si>
+    <t>20130417</t>
+  </si>
+  <si>
+    <t>GLO WSH&amp;SHN SHMPO700</t>
+  </si>
+  <si>
+    <t>10028422</t>
+  </si>
+  <si>
+    <t>KIT WIPER FLD PCH400</t>
+  </si>
+  <si>
+    <t>20001713</t>
+  </si>
+  <si>
+    <t>KIT BLACK MGC GEL180</t>
+  </si>
+  <si>
+    <t>20109707</t>
+  </si>
+  <si>
+    <t>KIT WATERLESS BTL500</t>
+  </si>
+  <si>
+    <t>20090436</t>
+  </si>
+  <si>
+    <t>KIT DETAILER SPRY200</t>
+  </si>
+  <si>
+    <t>20121376</t>
+  </si>
+  <si>
+    <t>KIT MOTOR B TO B 115</t>
+  </si>
+  <si>
+    <t>20013832</t>
+  </si>
+  <si>
+    <t>KIT MOTOR MLTGUNA100</t>
+  </si>
+  <si>
+    <t>20037676</t>
+  </si>
+  <si>
+    <t>KIT MTR CHN.LUBE 110</t>
+  </si>
+  <si>
+    <t>10016210</t>
+  </si>
+  <si>
+    <t>AMBI PUR VAN.BQT 7.5</t>
+  </si>
+  <si>
+    <t>10016209</t>
+  </si>
+  <si>
+    <t>AMBI/P C/FR.AQUA 7.5</t>
+  </si>
+  <si>
+    <t>20016897</t>
+  </si>
+  <si>
+    <t>GLADE CAR FRSH APL70</t>
+  </si>
+  <si>
+    <t>20124786</t>
+  </si>
+  <si>
+    <t>BAYFRESH CPUCCINO 70</t>
+  </si>
+  <si>
+    <t>13</t>
   </si>
   <si>
     <t>20039156</t>
@@ -67,387 +505,6 @@
     <t>IDM J/HJN DISP DWSA</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>10014035</t>
-  </si>
-  <si>
-    <t>BAGUS SK.LANTAI20920</t>
-  </si>
-  <si>
-    <t>10014036</t>
-  </si>
-  <si>
-    <t>BAGUS SKT.BAJU 20930</t>
-  </si>
-  <si>
-    <t>10006200</t>
-  </si>
-  <si>
-    <t>BAGUS SHOE BRSH 3354</t>
-  </si>
-  <si>
-    <t>20090053</t>
-  </si>
-  <si>
-    <t>BAGUS KAIN LAP SBGNA</t>
-  </si>
-  <si>
-    <t>20030983</t>
-  </si>
-  <si>
-    <t>IDM SERBET HANDUK</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20038032</t>
-  </si>
-  <si>
-    <t>IDM KAIN LAP PEL</t>
-  </si>
-  <si>
-    <t>20085916</t>
-  </si>
-  <si>
-    <t>IDM FOOD SVR 2'S 750</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20121395</t>
-  </si>
-  <si>
-    <t>KIIP RCTANGLR 10S 1L</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20092994</t>
-  </si>
-  <si>
-    <t>IDM CLING WRAP 30X30</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20062464</t>
-  </si>
-  <si>
-    <t>IDM TSK GIGI TRAVEL</t>
-  </si>
-  <si>
-    <t>20038650</t>
-  </si>
-  <si>
-    <t>IDM TUSUK GIGI 200'S</t>
-  </si>
-  <si>
-    <t>20026412</t>
-  </si>
-  <si>
-    <t>INDOMARET LAP MOTOR</t>
-  </si>
-  <si>
-    <t>20026410</t>
-  </si>
-  <si>
-    <t>INDOMARET LAP MOBIL</t>
-  </si>
-  <si>
-    <t>20036334</t>
-  </si>
-  <si>
-    <t>KEN/M MTR WASH SPNG</t>
-  </si>
-  <si>
-    <t>20075589</t>
-  </si>
-  <si>
-    <t>IDM LILIN PUTIH 8'S</t>
-  </si>
-  <si>
-    <t>20072837</t>
-  </si>
-  <si>
-    <t>IDM LILIN ULTAH 12'S</t>
-  </si>
-  <si>
-    <t>20142226</t>
-  </si>
-  <si>
-    <t>IDM KTG SMPH 44X60CM</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20084539</t>
-  </si>
-  <si>
-    <t>KRSBOW GLOVE LATEX</t>
-  </si>
-  <si>
-    <t>20128556</t>
-  </si>
-  <si>
-    <t>IDM PLSTK KLIP 15X10</t>
-  </si>
-  <si>
-    <t>20128557</t>
-  </si>
-  <si>
-    <t>IDM PLSTK KLIP 25X16</t>
-  </si>
-  <si>
-    <t>20082114</t>
-  </si>
-  <si>
-    <t>IDM PLSTK HDPE 15X30</t>
-  </si>
-  <si>
-    <t>20082115</t>
-  </si>
-  <si>
-    <t>IDM PLSTK HDPE 20X35</t>
-  </si>
-  <si>
-    <t>20086810</t>
-  </si>
-  <si>
-    <t>IDM LAP SERBAGUNA</t>
-  </si>
-  <si>
-    <t>20098808</t>
-  </si>
-  <si>
-    <t>BAGUS SRG TGN PLS100</t>
-  </si>
-  <si>
-    <t>20141993</t>
-  </si>
-  <si>
-    <t>LARISST SCRUB SPONGE</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20044863</t>
-  </si>
-  <si>
-    <t>IDM SABUT STNLSS 2'S</t>
-  </si>
-  <si>
-    <t>20139062</t>
-  </si>
-  <si>
-    <t>LARISST SABUT CUCI2S</t>
-  </si>
-  <si>
-    <t>10003530</t>
-  </si>
-  <si>
-    <t>S/B TOUGH CLN SCRB</t>
-  </si>
-  <si>
-    <t>20053561</t>
-  </si>
-  <si>
-    <t>SB EASY CLN SCRB SPG</t>
-  </si>
-  <si>
-    <t>20113117</t>
-  </si>
-  <si>
-    <t>SC.BRITE SBT.JRG M60</t>
-  </si>
-  <si>
-    <t>20129462</t>
-  </si>
-  <si>
-    <t>IDM SPGE MND LG PUFF</t>
-  </si>
-  <si>
-    <t>20033662</t>
-  </si>
-  <si>
-    <t>IDM SPONGE MANDI PCK</t>
-  </si>
-  <si>
-    <t>20133214</t>
-  </si>
-  <si>
-    <t>NXCARE BBL SHWR PUFF</t>
-  </si>
-  <si>
-    <t>20131332</t>
-  </si>
-  <si>
-    <t>AIRPRO A/F SKR LMI10</t>
-  </si>
-  <si>
-    <t>20080042</t>
-  </si>
-  <si>
-    <t>BYFRSH HANG'N GO CRV</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20101038</t>
-  </si>
-  <si>
-    <t>BYFRSH HANG'N GO LIM</t>
-  </si>
-  <si>
-    <t>20048540</t>
-  </si>
-  <si>
-    <t>STELLA DAILY/F ORG/B</t>
-  </si>
-  <si>
-    <t>20048539</t>
-  </si>
-  <si>
-    <t>STELLA DAILY/F RED/K</t>
-  </si>
-  <si>
-    <t>20130343</t>
-  </si>
-  <si>
-    <t>CLFORNIA A/F STRWBRY</t>
-  </si>
-  <si>
-    <t>20138691</t>
-  </si>
-  <si>
-    <t>STELLA CAR HANG JASM</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20138690</t>
-  </si>
-  <si>
-    <t>STELLA CAR HANG AQUA</t>
-  </si>
-  <si>
-    <t>20052689</t>
-  </si>
-  <si>
-    <t>AMBI PUR SKY/BR 2ML</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20111567</t>
-  </si>
-  <si>
-    <t>KAGUMI D.SCNT COFFEE</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20111568</t>
-  </si>
-  <si>
-    <t>KAGUMI D.SCNT T.MNGO</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20132836</t>
-  </si>
-  <si>
-    <t>AIRPRO A/F OCEAN 9ML</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>10005473</t>
-  </si>
-  <si>
-    <t>KIT WASH&amp;GLOW PCH720</t>
-  </si>
-  <si>
-    <t>20130417</t>
-  </si>
-  <si>
-    <t>GLO WSH&amp;SHN SHMPO700</t>
-  </si>
-  <si>
-    <t>10028422</t>
-  </si>
-  <si>
-    <t>KIT WIPER FLD PCH400</t>
-  </si>
-  <si>
-    <t>20001713</t>
-  </si>
-  <si>
-    <t>KIT BLACK MGC GEL180</t>
-  </si>
-  <si>
-    <t>20109707</t>
-  </si>
-  <si>
-    <t>KIT WATERLESS BTL500</t>
-  </si>
-  <si>
-    <t>20090436</t>
-  </si>
-  <si>
-    <t>KIT DETAILER SPRY200</t>
-  </si>
-  <si>
-    <t>20121376</t>
-  </si>
-  <si>
-    <t>KIT MOTOR B TO B 115</t>
-  </si>
-  <si>
-    <t>20013832</t>
-  </si>
-  <si>
-    <t>KIT MOTOR MLTGUNA100</t>
-  </si>
-  <si>
-    <t>20037676</t>
-  </si>
-  <si>
-    <t>KIT MTR CHN.LUBE 110</t>
-  </si>
-  <si>
-    <t>10016210</t>
-  </si>
-  <si>
-    <t>AMBI PUR VAN.BQT 7.5</t>
-  </si>
-  <si>
-    <t>10016209</t>
-  </si>
-  <si>
-    <t>AMBI/P C/FR.AQUA 7.5</t>
-  </si>
-  <si>
-    <t>20016897</t>
-  </si>
-  <si>
-    <t>GLADE CAR FRSH APL70</t>
-  </si>
-  <si>
     <t>20135615</t>
   </si>
   <si>
@@ -802,9 +859,6 @@
     <t>KRSBW HS/CLM B.FLY2S</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
     <t>20135301</t>
   </si>
   <si>
@@ -904,18 +958,18 @@
     <t>HANNOCHS C/D SNC 5W</t>
   </si>
   <si>
+    <t>20134457</t>
+  </si>
+  <si>
+    <t>IN-LITE LED BOX 15W</t>
+  </si>
+  <si>
     <t>20094959</t>
   </si>
   <si>
     <t>IN-LITE LED BOX 9W</t>
   </si>
   <si>
-    <t>20134457</t>
-  </si>
-  <si>
-    <t>IN-LITE LED BOX 15W</t>
-  </si>
-  <si>
     <t>20060010</t>
   </si>
   <si>
@@ -955,40 +1009,22 @@
     <t>16</t>
   </si>
   <si>
-    <t>20131331</t>
-  </si>
-  <si>
-    <t>AIRPRO A/F CLWV TD10</t>
-  </si>
-  <si>
-    <t>20124786</t>
-  </si>
-  <si>
-    <t>BAYFRESH CPUCCINO 70</t>
-  </si>
-  <si>
     <t>20076488</t>
   </si>
   <si>
     <t>IDM SAPU LIDI TABAH</t>
   </si>
   <si>
-    <t>20117814</t>
-  </si>
-  <si>
-    <t>BYFRSH H 'N GO SKR/B</t>
-  </si>
-  <si>
     <t>20071449</t>
   </si>
   <si>
     <t>IDM PAYUNG PJG WRNA</t>
   </si>
   <si>
-    <t>20117815</t>
-  </si>
-  <si>
-    <t>BYFRSH H 'N GO D/ICE</t>
+    <t>20126370</t>
+  </si>
+  <si>
+    <t>COOGER MOP CMO4609</t>
   </si>
   <si>
     <t>20126374</t>
@@ -997,208 +1033,154 @@
     <t>TOILETBRUSH GRAY WHT</t>
   </si>
   <si>
-    <t>20055262</t>
-  </si>
-  <si>
-    <t>STELLA DAILY/F DRM 7</t>
-  </si>
-  <si>
     <t>20035266</t>
   </si>
   <si>
     <t>INDOMARET PEL REFILL</t>
   </si>
   <si>
-    <t>20052690</t>
-  </si>
-  <si>
-    <t>AMBI PUR LVDR/C 2ML</t>
-  </si>
-  <si>
     <t>20032453</t>
   </si>
   <si>
     <t>KEN/M STP KNTK F1-4</t>
   </si>
   <si>
-    <t>20130339</t>
-  </si>
-  <si>
-    <t>CLFORNIA A/F NEWPORT</t>
-  </si>
-  <si>
     <t>20126378</t>
   </si>
   <si>
     <t>2PCS DETACBLE BROOM</t>
   </si>
   <si>
-    <t>20138849</t>
-  </si>
-  <si>
-    <t>AIRPRO ESS FRUITY 9</t>
+    <t>20037222</t>
+  </si>
+  <si>
+    <t>KEN/M RKT NYM+SNTR B</t>
+  </si>
+  <si>
+    <t>20011832</t>
+  </si>
+  <si>
+    <t>KEN/M REG+MTR PROTCN</t>
+  </si>
+  <si>
+    <t>20053613</t>
+  </si>
+  <si>
+    <t>IDM TALI TAMBANG 6MM</t>
+  </si>
+  <si>
+    <t>20074350</t>
+  </si>
+  <si>
+    <t>IDM PAYUNG LPT TIGA</t>
+  </si>
+  <si>
+    <t>20026807</t>
+  </si>
+  <si>
+    <t>KEN/M OBENG SET MN6</t>
+  </si>
+  <si>
+    <t>20060033</t>
+  </si>
+  <si>
+    <t>KEN/M WTR FLTR DAIYU</t>
+  </si>
+  <si>
+    <t>10016469</t>
+  </si>
+  <si>
+    <t>KEN/M GAS LIGHTER</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
-    <t>20126370</t>
-  </si>
-  <si>
-    <t>COOGER MOP CMO4609</t>
-  </si>
-  <si>
-    <t>20037222</t>
-  </si>
-  <si>
-    <t>KEN/M RKT NYM+SNTR B</t>
+    <t>20121040</t>
+  </si>
+  <si>
+    <t>KEN/M KRAN PLSTK PTH</t>
+  </si>
+  <si>
+    <t>20139712</t>
+  </si>
+  <si>
+    <t>IDM SANDAL JPT KRT38</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
-    <t>20011832</t>
-  </si>
-  <si>
-    <t>KEN/M REG+MTR PROTCN</t>
+    <t>20072320</t>
+  </si>
+  <si>
+    <t>IDM SNDAL PRIA 39-40</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
-    <t>20053613</t>
-  </si>
-  <si>
-    <t>IDM TALI TAMBANG 6MM</t>
+    <t>20072322</t>
+  </si>
+  <si>
+    <t>IDM SNDAL PRIA 41-42</t>
   </si>
   <si>
     <t>19</t>
   </si>
   <si>
-    <t>20074350</t>
-  </si>
-  <si>
-    <t>IDM PAYUNG LPT TIGA</t>
+    <t>20093212</t>
+  </si>
+  <si>
+    <t>IDM SANDAL JPT KRT42</t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
-    <t>20026807</t>
-  </si>
-  <si>
-    <t>KEN/M OBENG SET MN6</t>
+    <t>20093211</t>
+  </si>
+  <si>
+    <t>IDM SANDAL JPT KRT40</t>
   </si>
   <si>
     <t>21</t>
   </si>
   <si>
-    <t>20060033</t>
-  </si>
-  <si>
-    <t>KEN/M WTR FLTR DAIYU</t>
+    <t>20126380</t>
+  </si>
+  <si>
+    <t>30CLIP WINDPROF BSKT</t>
   </si>
   <si>
     <t>22</t>
   </si>
   <si>
-    <t>10016469</t>
-  </si>
-  <si>
-    <t>KEN/M GAS LIGHTER</t>
+    <t>20118405</t>
+  </si>
+  <si>
+    <t>CLARIS EMBER 12 TTP</t>
   </si>
   <si>
     <t>23</t>
   </si>
   <si>
-    <t>20121040</t>
-  </si>
-  <si>
-    <t>KEN/M KRAN PLSTK PTH</t>
+    <t>20127779</t>
+  </si>
+  <si>
+    <t>COOGER WALL SOAP W+G</t>
   </si>
   <si>
     <t>24</t>
   </si>
   <si>
-    <t>20139712</t>
-  </si>
-  <si>
-    <t>IDM SANDAL JPT KRT38</t>
+    <t>20126372</t>
+  </si>
+  <si>
+    <t>DISC MULTI TOOHBRUSH</t>
   </si>
   <si>
     <t>25</t>
-  </si>
-  <si>
-    <t>20072320</t>
-  </si>
-  <si>
-    <t>IDM SNDAL PRIA 39-40</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>20072322</t>
-  </si>
-  <si>
-    <t>IDM SNDAL PRIA 41-42</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>20093212</t>
-  </si>
-  <si>
-    <t>IDM SANDAL JPT KRT42</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>20093211</t>
-  </si>
-  <si>
-    <t>IDM SANDAL JPT KRT40</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>20126380</t>
-  </si>
-  <si>
-    <t>30CLIP WINDPROF BSKT</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>20118405</t>
-  </si>
-  <si>
-    <t>CLARIS EMBER 12 TTP</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>20127779</t>
-  </si>
-  <si>
-    <t>COOGER WALL SOAP W+G</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>20126372</t>
-  </si>
-  <si>
-    <t>DISC MULTI TOOHBRUSH</t>
-  </si>
-  <si>
-    <t>33</t>
   </si>
 </sst>
 </file>
@@ -1591,7 +1573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F177"/>
+  <dimension ref="A1:F178"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1678,7 +1660,7 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1815,7 +1797,7 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>5</v>
@@ -1823,10 +1805,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1835,7 +1817,7 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>5</v>
@@ -1995,7 +1977,7 @@
         <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>9</v>
@@ -2015,7 +1997,7 @@
         <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -2155,7 +2137,7 @@
         <v>15</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -2175,7 +2157,7 @@
         <v>15</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>9</v>
@@ -2212,7 +2194,7 @@
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>4</v>
@@ -2232,7 +2214,7 @@
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>8</v>
@@ -2252,7 +2234,7 @@
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>12</v>
@@ -2272,7 +2254,7 @@
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>15</v>
@@ -2292,10 +2274,10 @@
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>9</v>
@@ -2312,10 +2294,10 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>9</v>
@@ -2332,7 +2314,7 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>34</v>
@@ -2352,7 +2334,7 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>37</v>
@@ -2372,7 +2354,7 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>40</v>
@@ -2392,7 +2374,7 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>4</v>
@@ -2412,33 +2394,33 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="C42" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2452,13 +2434,13 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2472,13 +2454,13 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2492,13 +2474,13 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2512,90 +2494,90 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>106</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>106</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="F48" s="1" t="s">
-        <v>111</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F49" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>9</v>
@@ -2603,119 +2585,119 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>74</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F52" s="1" t="s">
-        <v>9</v>
+        <v>119</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E53" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F53" s="1" t="s">
-        <v>9</v>
+        <v>74</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>9</v>
+        <v>119</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>29</v>
+        <v>128</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>9</v>
@@ -2723,19 +2705,19 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>9</v>
@@ -2743,22 +2725,22 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="C58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="F58" s="1" t="s">
-        <v>9</v>
+        <v>74</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2775,7 +2757,7 @@
         <v>34</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>9</v>
@@ -2795,7 +2777,7 @@
         <v>34</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>9</v>
@@ -2815,10 +2797,10 @@
         <v>34</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>111</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2835,10 +2817,10 @@
         <v>34</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>117</v>
+        <v>15</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>111</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2855,7 +2837,7 @@
         <v>34</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>120</v>
+        <v>18</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>9</v>
@@ -2872,13 +2854,13 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>95</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2892,13 +2874,13 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>74</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2912,13 +2894,13 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E66" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="F66" s="1" t="s">
-        <v>95</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2932,10 +2914,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>9</v>
@@ -2952,13 +2934,13 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2972,53 +2954,53 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>157</v>
+        <v>112</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>12</v>
+        <v>134</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>157</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="C71" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C71" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F71" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -3032,13 +3014,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3052,13 +3034,13 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -3072,13 +3054,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3092,13 +3074,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3112,13 +3094,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>95</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3132,13 +3114,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3152,73 +3134,73 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>95</v>
+        <v>176</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F79" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>182</v>
+        <v>97</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3232,13 +3214,13 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3252,13 +3234,13 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3272,13 +3254,13 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3292,13 +3274,13 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3312,13 +3294,13 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3332,13 +3314,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3352,13 +3334,13 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3372,13 +3354,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3392,610 +3374,610 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>95</v>
+        <v>201</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>5</v>
+        <v>97</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>5</v>
+        <v>97</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>5</v>
+        <v>57</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>5</v>
+        <v>97</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>5</v>
+        <v>97</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>74</v>
+        <v>119</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>57</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>57</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>57</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>9</v>
+        <v>74</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>5</v>
+        <v>74</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>5</v>
+        <v>57</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>5</v>
+        <v>57</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>57</v>
@@ -4003,22 +3985,22 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>263</v>
+        <v>134</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>5</v>
+        <v>57</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4032,10 +4014,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>263</v>
+        <v>134</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>9</v>
@@ -4052,13 +4034,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>263</v>
+        <v>134</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>9</v>
+        <v>74</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4072,10 +4054,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>263</v>
+        <v>134</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>9</v>
@@ -4092,13 +4074,13 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>263</v>
+        <v>134</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4112,13 +4094,13 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>263</v>
+        <v>134</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4132,13 +4114,13 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>263</v>
+        <v>134</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -4152,7 +4134,7 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>263</v>
+        <v>134</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>37</v>
@@ -4172,13 +4154,13 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>263</v>
+        <v>134</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>40</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4192,13 +4174,13 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>263</v>
+        <v>161</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4212,110 +4194,110 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>284</v>
+        <v>161</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>284</v>
+        <v>161</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>284</v>
+        <v>161</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>290</v>
-      </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>284</v>
+        <v>161</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>292</v>
-      </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>284</v>
+        <v>161</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>294</v>
-      </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>284</v>
+        <v>161</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>9</v>
@@ -4323,39 +4305,39 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>296</v>
-      </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>284</v>
+        <v>161</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>298</v>
-      </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>284</v>
+        <v>161</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>9</v>
@@ -4363,19 +4345,19 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>284</v>
+        <v>161</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>40</v>
+        <v>128</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>9</v>
@@ -4383,22 +4365,22 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="E140" s="1" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4412,13 +4394,13 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>117</v>
+        <v>8</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4432,13 +4414,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4452,13 +4434,13 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>263</v>
+        <v>15</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>57</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4472,10 +4454,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>284</v>
+        <v>18</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4492,190 +4474,190 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>315</v>
-      </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>74</v>
+        <v>9</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>95</v>
+        <v>9</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>321</v>
-      </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>29</v>
+        <v>128</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>95</v>
+        <v>9</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>18</v>
+        <v>131</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>325</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>34</v>
+        <v>134</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>95</v>
+        <v>9</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>327</v>
-      </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>37</v>
+        <v>161</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>329</v>
-      </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>40</v>
+        <v>302</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B154" s="1" t="s">
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="C154" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="E154" s="1" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4692,13 +4674,13 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>117</v>
+        <v>8</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>111</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4712,13 +4694,13 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4732,10 +4714,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>263</v>
+        <v>15</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>9</v>
@@ -4752,10 +4734,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>284</v>
+        <v>18</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>9</v>
@@ -4772,30 +4754,30 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>342</v>
+        <v>31</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>313</v>
+        <v>34</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>9</v>
@@ -4803,19 +4785,19 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>347</v>
+        <v>37</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>9</v>
@@ -4823,19 +4805,19 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>350</v>
+        <v>40</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>9</v>
@@ -4843,39 +4825,39 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>353</v>
+        <v>128</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>356</v>
+        <v>131</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -4883,39 +4865,39 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>359</v>
+        <v>134</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>362</v>
+        <v>161</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>9</v>
@@ -4923,19 +4905,19 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>365</v>
+        <v>302</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>9</v>
@@ -4943,19 +4925,19 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>9</v>
@@ -4963,39 +4945,39 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>371</v>
+        <v>331</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5003,19 +4985,19 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5023,19 +5005,19 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5043,19 +5025,19 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5063,39 +5045,39 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>9</v>
@@ -5103,19 +5085,19 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>9</v>
@@ -5123,21 +5105,41 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="F177" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A178" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="F178" s="1" t="s">
         <v>9</v>
       </c>
     </row>

--- a/HNM03S.xlsx
+++ b/HNM03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="397">
   <si>
     <t/>
   </si>
@@ -70,6 +70,24 @@
     <t>5</t>
   </si>
   <si>
+    <t>20039156</t>
+  </si>
+  <si>
+    <t>IDM J/HJN DISP DWSA</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20143597</t>
+  </si>
+  <si>
+    <t>IDM JAS HJN PNCO CLN</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>10014035</t>
   </si>
   <si>
@@ -115,18 +133,12 @@
     <t>IDM FOOD SVR 2'S 750</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>20121395</t>
   </si>
   <si>
     <t>KIIP RCTANGLR 10S 1L</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>20092994</t>
   </si>
   <si>
@@ -286,25 +298,103 @@
     <t>NXCARE BBL SHWR PUFF</t>
   </si>
   <si>
+    <t>20131332</t>
+  </si>
+  <si>
+    <t>AIRPRO A/F SKR LMI10</t>
+  </si>
+  <si>
+    <t>20080042</t>
+  </si>
+  <si>
+    <t>BYFRSH HANG'N GO CRV</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20101038</t>
+  </si>
+  <si>
+    <t>BYFRSH HANG'N GO LIM</t>
+  </si>
+  <si>
+    <t>20048540</t>
+  </si>
+  <si>
+    <t>STELLA DAILY/F ORG/B</t>
+  </si>
+  <si>
+    <t>20048539</t>
+  </si>
+  <si>
+    <t>STELLA DAILY/F RED/K</t>
+  </si>
+  <si>
+    <t>20130343</t>
+  </si>
+  <si>
+    <t>CLFORNIA A/F STRWBRY</t>
+  </si>
+  <si>
+    <t>20138691</t>
+  </si>
+  <si>
+    <t>STELLA CAR HANG JASM</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20138690</t>
+  </si>
+  <si>
+    <t>STELLA CAR HANG AQUA</t>
+  </si>
+  <si>
+    <t>20052689</t>
+  </si>
+  <si>
+    <t>AMBI PUR SKY/BR 2ML</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20111567</t>
+  </si>
+  <si>
+    <t>KAGUMI D.SCNT COFFEE</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20111568</t>
+  </si>
+  <si>
+    <t>KAGUMI D.SCNT T.MNGO</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20132836</t>
+  </si>
+  <si>
+    <t>AIRPRO A/F OCEAN 9ML</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
     <t>20131331</t>
   </si>
   <si>
     <t>AIRPRO A/F CLWV TD10</t>
   </si>
   <si>
-    <t>20131332</t>
-  </si>
-  <si>
-    <t>AIRPRO A/F SKR LMI10</t>
-  </si>
-  <si>
-    <t>20080042</t>
-  </si>
-  <si>
-    <t>BYFRSH HANG'N GO CRV</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
+    <t>13</t>
   </si>
   <si>
     <t>20117814</t>
@@ -313,10 +403,7 @@
     <t>BYFRSH H 'N GO SKR/B</t>
   </si>
   <si>
-    <t>20101038</t>
-  </si>
-  <si>
-    <t>BYFRSH HANG'N GO LIM</t>
+    <t>14</t>
   </si>
   <si>
     <t>20117815</t>
@@ -325,10 +412,7 @@
     <t>BYFRSH H 'N GO D/ICE</t>
   </si>
   <si>
-    <t>20048540</t>
-  </si>
-  <si>
-    <t>STELLA DAILY/F ORG/B</t>
+    <t>15</t>
   </si>
   <si>
     <t>20055262</t>
@@ -337,10 +421,7 @@
     <t>STELLA DAILY/F DRM 7</t>
   </si>
   <si>
-    <t>20048539</t>
-  </si>
-  <si>
-    <t>STELLA DAILY/F RED/K</t>
+    <t>16</t>
   </si>
   <si>
     <t>20052690</t>
@@ -349,7 +430,7 @@
     <t>AMBI PUR LVDR/C 2ML</t>
   </si>
   <si>
-    <t>PT,(E-3B)</t>
+    <t>17</t>
   </si>
   <si>
     <t>20130339</t>
@@ -358,19 +439,7 @@
     <t>CLFORNIA A/F NEWPORT</t>
   </si>
   <si>
-    <t>20130343</t>
-  </si>
-  <si>
-    <t>CLFORNIA A/F STRWBRY</t>
-  </si>
-  <si>
-    <t>20138691</t>
-  </si>
-  <si>
-    <t>STELLA CAR HANG JASM</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
+    <t>18</t>
   </si>
   <si>
     <t>20138849</t>
@@ -379,43 +448,7 @@
     <t>AIRPRO ESS FRUITY 9</t>
   </si>
   <si>
-    <t>20138690</t>
-  </si>
-  <si>
-    <t>STELLA CAR HANG AQUA</t>
-  </si>
-  <si>
-    <t>20052689</t>
-  </si>
-  <si>
-    <t>AMBI PUR SKY/BR 2ML</t>
-  </si>
-  <si>
-    <t>20111567</t>
-  </si>
-  <si>
-    <t>KAGUMI D.SCNT COFFEE</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20111568</t>
-  </si>
-  <si>
-    <t>KAGUMI D.SCNT T.MNGO</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20132836</t>
-  </si>
-  <si>
-    <t>AIRPRO A/F OCEAN 9ML</t>
-  </si>
-  <si>
-    <t>12</t>
+    <t>19</t>
   </si>
   <si>
     <t>10005473</t>
@@ -496,15 +529,6 @@
     <t>BAYFRESH CPUCCINO 70</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20039156</t>
-  </si>
-  <si>
-    <t>IDM J/HJN DISP DWSA</t>
-  </si>
-  <si>
     <t>20135615</t>
   </si>
   <si>
@@ -610,6 +634,123 @@
     <t>WHKAS T/M TNA KNKM70</t>
   </si>
   <si>
+    <t>20121357</t>
+  </si>
+  <si>
+    <t>ME-O OCEAN FISH 80G</t>
+  </si>
+  <si>
+    <t>20096777</t>
+  </si>
+  <si>
+    <t>WHISKAS OCEAN FSH 80</t>
+  </si>
+  <si>
+    <t>20113920</t>
+  </si>
+  <si>
+    <t>ME-O TUNA IN JLY 80G</t>
+  </si>
+  <si>
+    <t>20117626</t>
+  </si>
+  <si>
+    <t>WHKAS T/M CHK TUNA70</t>
+  </si>
+  <si>
+    <t>20031232</t>
+  </si>
+  <si>
+    <t>WHISKAS CF TUNA 80</t>
+  </si>
+  <si>
+    <t>20102393</t>
+  </si>
+  <si>
+    <t>ME-O KTN OCN.FISH 50</t>
+  </si>
+  <si>
+    <t>20140134</t>
+  </si>
+  <si>
+    <t>CUTIES CATZ TUNA 75G</t>
+  </si>
+  <si>
+    <t>20031233</t>
+  </si>
+  <si>
+    <t>WHISKAS CF MAC&amp;SAL80</t>
+  </si>
+  <si>
+    <t>20104599</t>
+  </si>
+  <si>
+    <t>ME-O CRM TRT SLMN 60</t>
+  </si>
+  <si>
+    <t>20128696</t>
+  </si>
+  <si>
+    <t>LIFE CAT KTEN TUNA85</t>
+  </si>
+  <si>
+    <t>20104595</t>
+  </si>
+  <si>
+    <t>ME-O CRM CHKN&amp;LVR 60</t>
+  </si>
+  <si>
+    <t>20126940</t>
+  </si>
+  <si>
+    <t>K/B CAT FD SLMON 120</t>
+  </si>
+  <si>
+    <t>20135980</t>
+  </si>
+  <si>
+    <t>IDM CAT FOOD TUNA 80</t>
+  </si>
+  <si>
+    <t>20128695</t>
+  </si>
+  <si>
+    <t>BIO CREAMY TUNA 4S</t>
+  </si>
+  <si>
+    <t>20135431</t>
+  </si>
+  <si>
+    <t>DELI CRMY TUNA 2X14G</t>
+  </si>
+  <si>
+    <t>20143751</t>
+  </si>
+  <si>
+    <t>MEO TUNA CHKN JLY 80</t>
+  </si>
+  <si>
+    <t>PT,(E-13B)</t>
+  </si>
+  <si>
+    <t>20134232</t>
+  </si>
+  <si>
+    <t>SH CRMY TREATS 4X15G</t>
+  </si>
+  <si>
+    <t>20135432</t>
+  </si>
+  <si>
+    <t>DELI CRM TN&amp;SLMN2X14</t>
+  </si>
+  <si>
+    <t>20143750</t>
+  </si>
+  <si>
+    <t>MEO KTEN TUNA SRDN80</t>
+  </si>
+  <si>
     <t>20121362</t>
   </si>
   <si>
@@ -619,114 +760,12 @@
     <t>RT,(E-9B)</t>
   </si>
   <si>
-    <t>20096777</t>
-  </si>
-  <si>
-    <t>WHISKAS OCEAN FSH 80</t>
-  </si>
-  <si>
-    <t>20117626</t>
-  </si>
-  <si>
-    <t>WHKAS T/M CHK TUNA70</t>
-  </si>
-  <si>
-    <t>20121357</t>
-  </si>
-  <si>
-    <t>ME-O OCEAN FISH 80G</t>
-  </si>
-  <si>
-    <t>20031232</t>
-  </si>
-  <si>
-    <t>WHISKAS CF TUNA 80</t>
-  </si>
-  <si>
-    <t>20113920</t>
-  </si>
-  <si>
-    <t>ME-O TUNA IN JLY 80G</t>
-  </si>
-  <si>
-    <t>20140134</t>
-  </si>
-  <si>
-    <t>CUTIES CATZ TUNA 75G</t>
-  </si>
-  <si>
-    <t>20031233</t>
-  </si>
-  <si>
-    <t>WHISKAS CF MAC&amp;SAL80</t>
-  </si>
-  <si>
     <t>20121808</t>
   </si>
   <si>
     <t>ME-O OTAK2 WF&amp;CS 80G</t>
   </si>
   <si>
-    <t>20128696</t>
-  </si>
-  <si>
-    <t>LIFE CAT KTEN TUNA85</t>
-  </si>
-  <si>
-    <t>20102393</t>
-  </si>
-  <si>
-    <t>ME-O KTN OCN.FISH 50</t>
-  </si>
-  <si>
-    <t>20126940</t>
-  </si>
-  <si>
-    <t>K/B CAT FD SLMON 120</t>
-  </si>
-  <si>
-    <t>20135980</t>
-  </si>
-  <si>
-    <t>IDM CAT FOOD TUNA 80</t>
-  </si>
-  <si>
-    <t>20104599</t>
-  </si>
-  <si>
-    <t>ME-O CRM TRT SLMN 60</t>
-  </si>
-  <si>
-    <t>20128695</t>
-  </si>
-  <si>
-    <t>BIO CREAMY TUNA 4S</t>
-  </si>
-  <si>
-    <t>20135431</t>
-  </si>
-  <si>
-    <t>DELI CRMY TUNA 2X14G</t>
-  </si>
-  <si>
-    <t>20104595</t>
-  </si>
-  <si>
-    <t>ME-O CRM CHKN&amp;LVR 60</t>
-  </si>
-  <si>
-    <t>20134232</t>
-  </si>
-  <si>
-    <t>SH CRMY TREATS 4X15G</t>
-  </si>
-  <si>
-    <t>20135432</t>
-  </si>
-  <si>
-    <t>DELI CRM TN&amp;SLMN2X14</t>
-  </si>
-  <si>
     <t>20098413</t>
   </si>
   <si>
@@ -775,6 +814,54 @@
     <t>IDM DUCKBILL PTIH 4S</t>
   </si>
   <si>
+    <t>20115472</t>
+  </si>
+  <si>
+    <t>IDM MASK 4D HTM 4'S</t>
+  </si>
+  <si>
+    <t>20117862</t>
+  </si>
+  <si>
+    <t>IDM MASKER PCK 5'S</t>
+  </si>
+  <si>
+    <t>20118218</t>
+  </si>
+  <si>
+    <t>IDM MSK SLIM HTM 5S</t>
+  </si>
+  <si>
+    <t>20071626</t>
+  </si>
+  <si>
+    <t>XANDER GEMBOK 50MM</t>
+  </si>
+  <si>
+    <t>20097529</t>
+  </si>
+  <si>
+    <t>KRSBOW PADLOCK 21031</t>
+  </si>
+  <si>
+    <t>20101650</t>
+  </si>
+  <si>
+    <t>B6.ESS BAG HLDR HOOK</t>
+  </si>
+  <si>
+    <t>20038033</t>
+  </si>
+  <si>
+    <t>IDM TALI RAFIA</t>
+  </si>
+  <si>
+    <t>20142274</t>
+  </si>
+  <si>
+    <t>IDM ADHESIVE HOOKS 3</t>
+  </si>
+  <si>
     <t>20131301</t>
   </si>
   <si>
@@ -787,18 +874,6 @@
     <t>IDM MASKER 4D PTH 4S</t>
   </si>
   <si>
-    <t>20115472</t>
-  </si>
-  <si>
-    <t>IDM MASK 4D HTM 4'S</t>
-  </si>
-  <si>
-    <t>20117862</t>
-  </si>
-  <si>
-    <t>IDM MASKER PCK 5'S</t>
-  </si>
-  <si>
     <t>20120506</t>
   </si>
   <si>
@@ -811,48 +886,12 @@
     <t>NXCARE CRBN MASK 2'S</t>
   </si>
   <si>
-    <t>20118218</t>
-  </si>
-  <si>
-    <t>IDM MSK SLIM HTM 5S</t>
-  </si>
-  <si>
-    <t>20071626</t>
-  </si>
-  <si>
-    <t>XANDER GEMBOK 50MM</t>
-  </si>
-  <si>
     <t>20142764</t>
   </si>
   <si>
     <t>IDM MSKR SLIM PTH 5S</t>
   </si>
   <si>
-    <t>20097529</t>
-  </si>
-  <si>
-    <t>KRSBOW PADLOCK 21031</t>
-  </si>
-  <si>
-    <t>20101650</t>
-  </si>
-  <si>
-    <t>B6.ESS BAG HLDR HOOK</t>
-  </si>
-  <si>
-    <t>20038033</t>
-  </si>
-  <si>
-    <t>IDM TALI RAFIA</t>
-  </si>
-  <si>
-    <t>20142274</t>
-  </si>
-  <si>
-    <t>IDM ADHESIVE HOOKS 3</t>
-  </si>
-  <si>
     <t>20126285</t>
   </si>
   <si>
@@ -919,9 +958,6 @@
     <t>PHILIPS LED E27 13WT</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
     <t>20123181</t>
   </si>
   <si>
@@ -1006,9 +1042,6 @@
     <t>INDOMARET ALAT PEL</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
     <t>20076488</t>
   </si>
   <si>
@@ -1093,9 +1126,6 @@
     <t>KEN/M GAS LIGHTER</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>20121040</t>
   </si>
   <si>
@@ -1108,25 +1138,16 @@
     <t>IDM SANDAL JPT KRT38</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>20072320</t>
   </si>
   <si>
     <t>IDM SNDAL PRIA 39-40</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
     <t>20072322</t>
   </si>
   <si>
     <t>IDM SNDAL PRIA 41-42</t>
-  </si>
-  <si>
-    <t>19</t>
   </si>
   <si>
     <t>20093212</t>
@@ -1573,14 +1594,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F178"/>
+  <dimension ref="A1:F181"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1714,41 +1735,38 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -1757,7 +1775,7 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>9</v>
@@ -1765,10 +1783,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -1777,7 +1795,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>9</v>
@@ -1785,10 +1803,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -1797,18 +1815,18 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1817,18 +1835,18 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -1837,7 +1855,7 @@
         <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -1860,7 +1878,7 @@
         <v>37</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1877,50 +1895,50 @@
         <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1937,10 +1955,10 @@
         <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1957,10 +1975,10 @@
         <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1977,7 +1995,7 @@
         <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>9</v>
@@ -1997,10 +2015,10 @@
         <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2017,10 +2035,10 @@
         <v>12</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2040,15 +2058,15 @@
         <v>37</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>57</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -2057,7 +2075,7 @@
         <v>12</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -2065,22 +2083,22 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2094,10 +2112,10 @@
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -2117,7 +2135,7 @@
         <v>15</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -2137,7 +2155,7 @@
         <v>15</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -2157,10 +2175,10 @@
         <v>15</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2177,10 +2195,10 @@
         <v>15</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2194,41 +2212,41 @@
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>74</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>76</v>
-      </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -2237,10 +2255,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2257,10 +2275,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2277,10 +2295,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2297,7 +2315,7 @@
         <v>18</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>9</v>
@@ -2317,10 +2335,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2340,7 +2358,7 @@
         <v>37</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2357,10 +2375,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2374,13 +2392,13 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2394,13 +2412,13 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>74</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2414,33 +2432,33 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2454,13 +2472,13 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2474,13 +2492,13 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2494,10 +2512,10 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>9</v>
@@ -2514,10 +2532,10 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>9</v>
@@ -2534,33 +2552,33 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>9</v>
+        <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F49" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2574,30 +2592,30 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>9</v>
+        <v>115</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>9</v>
@@ -2605,119 +2623,119 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>34</v>
+        <v>121</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>119</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>34</v>
+        <v>124</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>37</v>
+        <v>127</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>9</v>
+        <v>99</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>9</v>
@@ -2725,39 +2743,39 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>74</v>
+        <v>115</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>4</v>
+        <v>142</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>9</v>
@@ -2765,39 +2783,39 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>8</v>
+        <v>145</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>9</v>
+        <v>78</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>9</v>
@@ -2805,19 +2823,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>9</v>
@@ -2825,19 +2843,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>9</v>
@@ -2845,19 +2863,19 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>9</v>
@@ -2865,19 +2883,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>9</v>
@@ -2885,16 +2903,16 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>37</v>
@@ -2905,19 +2923,19 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>9</v>
@@ -2925,939 +2943,939 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>128</v>
+        <v>24</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>9</v>
+        <v>115</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>161</v>
+        <v>121</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>8</v>
+        <v>127</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>9</v>
+        <v>99</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>176</v>
+        <v>99</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>97</v>
+        <v>184</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>128</v>
+        <v>44</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>201</v>
+        <v>99</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>97</v>
+        <v>239</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B109" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F109" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>5</v>
+        <v>248</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>12</v>
+        <v>118</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3865,239 +3883,239 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>57</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>9</v>
+        <v>78</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>74</v>
+        <v>9</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>57</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -4105,99 +4123,99 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>5</v>
+        <v>61</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>37</v>
+        <v>118</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>40</v>
+        <v>121</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>161</v>
+        <v>124</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>5</v>
+        <v>61</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>161</v>
+        <v>124</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>8</v>
+        <v>127</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>9</v>
@@ -4205,59 +4223,59 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>161</v>
+        <v>124</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>9</v>
@@ -4265,19 +4283,19 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>9</v>
@@ -4285,19 +4303,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>9</v>
@@ -4305,39 +4323,39 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>9</v>
@@ -4345,19 +4363,19 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>128</v>
+        <v>21</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>9</v>
@@ -4365,19 +4383,19 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>302</v>
+        <v>127</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>5</v>
@@ -4385,59 +4403,59 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>302</v>
+        <v>127</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>302</v>
+        <v>127</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>12</v>
+        <v>118</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>302</v>
+        <v>130</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4445,19 +4463,19 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>302</v>
+        <v>130</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4465,79 +4483,79 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>302</v>
+        <v>130</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>302</v>
+        <v>130</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>302</v>
+        <v>130</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>302</v>
+        <v>130</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>9</v>
@@ -4545,19 +4563,19 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>302</v>
+        <v>130</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>128</v>
+        <v>21</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>9</v>
@@ -4565,19 +4583,19 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>302</v>
+        <v>130</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>131</v>
+        <v>24</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>9</v>
@@ -4585,19 +4603,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>302</v>
+        <v>130</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>134</v>
+        <v>44</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>9</v>
@@ -4605,99 +4623,99 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>302</v>
+        <v>130</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>161</v>
+        <v>118</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>302</v>
+        <v>130</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>302</v>
+        <v>121</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>331</v>
+        <v>130</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>331</v>
+        <v>130</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>8</v>
+        <v>127</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>5</v>
+        <v>61</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>331</v>
+        <v>130</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4705,59 +4723,59 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4765,19 +4783,19 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>9</v>
@@ -4785,19 +4803,19 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>9</v>
@@ -4805,39 +4823,39 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>128</v>
+        <v>21</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>9</v>
@@ -4845,59 +4863,59 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>131</v>
+        <v>24</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>134</v>
+        <v>44</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>161</v>
+        <v>118</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>9</v>
@@ -4905,59 +4923,59 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>302</v>
+        <v>121</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>360</v>
+        <v>124</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>331</v>
+        <v>127</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>9</v>
@@ -4965,79 +4983,79 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>365</v>
+        <v>130</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>368</v>
+        <v>133</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>371</v>
+        <v>136</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>374</v>
+        <v>139</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5054,10 +5072,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>377</v>
+        <v>142</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5065,81 +5083,141 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="B175" s="1" t="s">
-        <v>379</v>
-      </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>331</v>
+        <v>136</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>380</v>
+        <v>145</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E176" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="E176" s="1" t="s">
-        <v>383</v>
-      </c>
       <c r="F176" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E177" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="E177" s="1" t="s">
-        <v>386</v>
-      </c>
       <c r="F177" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E178" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="F178" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A179" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="E178" s="1" t="s">
+      <c r="B179" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="F178" s="1" t="s">
+      <c r="C179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A180" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A181" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="F181" s="1" t="s">
         <v>9</v>
       </c>
     </row>

--- a/HNM03S.xlsx
+++ b/HNM03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="397">
   <si>
     <t/>
   </si>
@@ -1744,7 +1744,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
@@ -1759,6 +1759,9 @@
       </c>
       <c r="E8" s="1" t="s">
         <v>24</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">

--- a/HNM03S.xlsx
+++ b/HNM03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="395">
   <si>
     <t/>
   </si>
@@ -974,12 +974,6 @@
   </si>
   <si>
     <t>PHILIP LED C/DYL 6W</t>
-  </si>
-  <si>
-    <t>20052902</t>
-  </si>
-  <si>
-    <t>PHILIPS LED C/DYL 4W</t>
   </si>
   <si>
     <t>20101464</t>
@@ -1594,7 +1588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F181"/>
+  <dimension ref="A1:F180"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4538,10 +4532,10 @@
         <v>130</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4558,7 +4552,7 @@
         <v>130</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>9</v>
@@ -4578,7 +4572,7 @@
         <v>130</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>9</v>
@@ -4598,7 +4592,7 @@
         <v>130</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>9</v>
@@ -4618,7 +4612,7 @@
         <v>130</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>9</v>
@@ -4638,7 +4632,7 @@
         <v>130</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>9</v>
@@ -4658,7 +4652,7 @@
         <v>130</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>9</v>
@@ -4678,10 +4672,10 @@
         <v>130</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -4698,10 +4692,10 @@
         <v>130</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>61</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4715,10 +4709,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>130</v>
+        <v>4</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4738,7 +4732,7 @@
         <v>136</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4758,7 +4752,7 @@
         <v>136</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4778,10 +4772,10 @@
         <v>136</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -4798,7 +4792,7 @@
         <v>136</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>9</v>
@@ -4818,10 +4812,10 @@
         <v>136</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4838,10 +4832,10 @@
         <v>136</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -4858,7 +4852,7 @@
         <v>136</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>9</v>
@@ -4878,7 +4872,7 @@
         <v>136</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>9</v>
@@ -4898,7 +4892,7 @@
         <v>136</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>9</v>
@@ -4918,10 +4912,10 @@
         <v>136</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -4938,7 +4932,7 @@
         <v>136</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -4958,10 +4952,10 @@
         <v>136</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -4978,7 +4972,7 @@
         <v>136</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>9</v>
@@ -4998,7 +4992,7 @@
         <v>136</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>9</v>
@@ -5018,7 +5012,7 @@
         <v>136</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>9</v>
@@ -5038,10 +5032,10 @@
         <v>136</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5058,7 +5052,7 @@
         <v>136</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5078,7 +5072,7 @@
         <v>136</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5098,7 +5092,7 @@
         <v>136</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>145</v>
+        <v>379</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5106,10 +5100,10 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
@@ -5118,7 +5112,7 @@
         <v>136</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5126,10 +5120,10 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
@@ -5138,18 +5132,18 @@
         <v>136</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
@@ -5158,7 +5152,7 @@
         <v>136</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>9</v>
@@ -5166,10 +5160,10 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
@@ -5178,7 +5172,7 @@
         <v>136</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>9</v>
@@ -5186,10 +5180,10 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
@@ -5198,29 +5192,9 @@
         <v>136</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A181" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="B181" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="C181" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E181" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="F181" s="1" t="s">
         <v>9</v>
       </c>
     </row>

--- a/HNM03S.xlsx
+++ b/HNM03S.xlsx
@@ -730,7 +730,7 @@
     <t>MEO TUNA CHKN JLY 80</t>
   </si>
   <si>
-    <t>PT,(E-13B)</t>
+    <t>RT,(E-13B)</t>
   </si>
   <si>
     <t>20134232</t>
